--- a/research/traditional_assets/database/data/malaysia/malaysia_coal_related_energy.xlsx
+++ b/research/traditional_assets/database/data/malaysia/malaysia_coal_related_energy.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="klse_hhgroup" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,22 +590,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>-0.1236180904522613</v>
+        <v>0.1552380952380952</v>
       </c>
       <c r="H2">
-        <v>-0.1236180904522613</v>
+        <v>0.1552380952380952</v>
       </c>
       <c r="I2">
-        <v>-0.0592964824120603</v>
+        <v>0.1514285714285714</v>
       </c>
       <c r="J2">
-        <v>-0.0592964824120603</v>
+        <v>0.1482649228705566</v>
       </c>
       <c r="K2">
-        <v>-2.22</v>
+        <v>3.66</v>
       </c>
       <c r="L2">
-        <v>-0.1115577889447236</v>
+        <v>0.1161904761904762</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -612,7 +614,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -621,79 +623,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>3.66</v>
+        <v>9.9</v>
       </c>
       <c r="V2">
-        <v>0.1413127413127413</v>
+        <v>0.1155192532088681</v>
       </c>
       <c r="W2">
-        <v>-0.2894393741851369</v>
+        <v>0.3075630252100841</v>
       </c>
       <c r="X2">
-        <v>0.07776375547624856</v>
+        <v>0.1557942453999314</v>
       </c>
       <c r="Y2">
-        <v>-0.3672031296613855</v>
+        <v>0.1517687798101527</v>
       </c>
       <c r="Z2">
-        <v>1.390635918937806</v>
+        <v>2.64928511354079</v>
       </c>
       <c r="AA2">
-        <v>-0.0824598183088749</v>
+        <v>0.3927960530212392</v>
       </c>
       <c r="AB2">
-        <v>0.07202792966482338</v>
+        <v>0.1462563201726772</v>
       </c>
       <c r="AC2">
-        <v>-0.1544877479736983</v>
+        <v>0.246539732848562</v>
       </c>
       <c r="AD2">
-        <v>3.65</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>3.65</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="AG2">
-        <v>-0.01000000000000023</v>
+        <v>-0.8600000000000012</v>
       </c>
       <c r="AH2">
-        <v>0.1235194585448393</v>
+        <v>0.09541904158750263</v>
       </c>
       <c r="AI2">
-        <v>0.2332268370607029</v>
+        <v>0.2052679382379655</v>
       </c>
       <c r="AJ2">
-        <v>-0.0003862495171881125</v>
+        <v>-0.01013672795851015</v>
       </c>
       <c r="AK2">
-        <v>-0.000834028356964156</v>
+        <v>-0.02519039250146459</v>
       </c>
       <c r="AL2">
-        <v>0.446</v>
+        <v>0.25</v>
       </c>
       <c r="AM2">
-        <v>0.446</v>
+        <v>0.25</v>
       </c>
       <c r="AN2">
-        <v>-28.96825396825397</v>
+        <v>1.460420032310177</v>
       </c>
       <c r="AO2">
-        <v>-2.645739910313901</v>
+        <v>19.08</v>
       </c>
       <c r="AP2">
-        <v>0.07936507936508119</v>
+        <v>-0.1389337641357029</v>
       </c>
       <c r="AQ2">
-        <v>-2.645739910313901</v>
+        <v>19.08</v>
       </c>
     </row>
     <row r="3">
@@ -713,22 +715,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>-0.1236180904522613</v>
+        <v>0.1552380952380952</v>
       </c>
       <c r="H3">
-        <v>-0.1236180904522613</v>
+        <v>0.1552380952380952</v>
       </c>
       <c r="I3">
-        <v>-0.0592964824120603</v>
+        <v>0.1514285714285714</v>
       </c>
       <c r="J3">
-        <v>-0.0592964824120603</v>
+        <v>0.1482649228705566</v>
       </c>
       <c r="K3">
-        <v>-2.22</v>
+        <v>3.66</v>
       </c>
       <c r="L3">
-        <v>-0.1115577889447236</v>
+        <v>0.1161904761904762</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -737,7 +739,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -746,79 +748,8791 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>3.66</v>
+        <v>9.9</v>
       </c>
       <c r="V3">
-        <v>0.1413127413127413</v>
+        <v>0.1155192532088681</v>
       </c>
       <c r="W3">
-        <v>-0.2894393741851369</v>
+        <v>0.3075630252100841</v>
       </c>
       <c r="X3">
-        <v>0.07776375547624856</v>
+        <v>0.1557942453999314</v>
       </c>
       <c r="Y3">
-        <v>-0.3672031296613855</v>
+        <v>0.1517687798101527</v>
       </c>
       <c r="Z3">
-        <v>1.390635918937806</v>
+        <v>2.64928511354079</v>
       </c>
       <c r="AA3">
-        <v>-0.0824598183088749</v>
+        <v>0.3927960530212392</v>
       </c>
       <c r="AB3">
-        <v>0.07202792966482338</v>
+        <v>0.1462563201726772</v>
       </c>
       <c r="AC3">
-        <v>-0.1544877479736983</v>
+        <v>0.246539732848562</v>
       </c>
       <c r="AD3">
-        <v>3.65</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>3.65</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="AG3">
-        <v>-0.01000000000000023</v>
+        <v>-0.8600000000000012</v>
       </c>
       <c r="AH3">
-        <v>0.1235194585448393</v>
+        <v>0.09541904158750263</v>
       </c>
       <c r="AI3">
-        <v>0.2332268370607029</v>
+        <v>0.2052679382379655</v>
       </c>
       <c r="AJ3">
-        <v>-0.0003862495171881125</v>
+        <v>-0.01013672795851015</v>
       </c>
       <c r="AK3">
-        <v>-0.000834028356964156</v>
+        <v>-0.02519039250146459</v>
       </c>
       <c r="AL3">
-        <v>0.446</v>
+        <v>0.25</v>
       </c>
       <c r="AM3">
-        <v>0.446</v>
+        <v>0.25</v>
       </c>
       <c r="AN3">
-        <v>-28.96825396825397</v>
+        <v>1.460420032310177</v>
       </c>
       <c r="AO3">
-        <v>-2.645739910313901</v>
+        <v>19.08</v>
       </c>
       <c r="AP3">
-        <v>0.07936507936508119</v>
+        <v>-0.1389337641357029</v>
       </c>
       <c r="AQ3">
-        <v>-2.645739910313901</v>
+        <v>19.08</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Heng Huat Resources Group Berhad (KLSE:HHGROUP)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>KLSE:HHGROUP</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Coal &amp; Related Energy</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.0954190415875026</v>
+      </c>
+      <c r="F2">
+        <v>0.2</v>
+      </c>
+      <c r="G2">
+        <v>85.7</v>
+      </c>
+      <c r="H2">
+        <v>78.8547981795124</v>
+      </c>
+      <c r="I2">
+        <v>84.84</v>
+      </c>
+      <c r="J2">
+        <v>87.9027981795124</v>
+      </c>
+      <c r="K2">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="L2">
+        <v>18.948</v>
+      </c>
+      <c r="M2">
+        <v>0.146256320172677</v>
+      </c>
+      <c r="N2">
+        <v>0.142512218407795</v>
+      </c>
+      <c r="O2">
+        <v>0.0558359449541284</v>
+      </c>
+      <c r="P2">
+        <v>0.0418</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.155794245399931</v>
+      </c>
+      <c r="T2">
+        <v>0.167690273009744</v>
+      </c>
+      <c r="U2">
+        <v>1.46547008099568</v>
+      </c>
+      <c r="V2">
+        <v>1.61447973942191</v>
+      </c>
+      <c r="W2">
+        <v>4.577120156600839</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>85.7</v>
+      </c>
+      <c r="AB2">
+        <v>0.07983393650755573</v>
+      </c>
+      <c r="AC2">
+        <v>0.07346834862385321</v>
+      </c>
+      <c r="AD2">
+        <v>0.24</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>6.19</v>
+      </c>
+      <c r="AH2">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="AI2">
+        <v>-0.01899999999999946</v>
+      </c>
+      <c r="AJ2">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="AK2">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="AL2">
+        <v>0.25</v>
+      </c>
+      <c r="AM2">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="AN2">
+        <v>9.9</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1471111537897008</v>
+      </c>
+      <c r="C2">
+        <v>94.0704098282519</v>
+      </c>
+      <c r="D2">
+        <v>84.17040982825189</v>
+      </c>
+      <c r="E2">
+        <v>-9.039999999999999</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>9.9</v>
+      </c>
+      <c r="H2">
+        <v>85.7</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>6.19</v>
+      </c>
+      <c r="K2">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L2">
+        <v>4.77</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>4.77</v>
+      </c>
+      <c r="O2">
+        <v>1.1448</v>
+      </c>
+      <c r="P2">
+        <v>3.6252</v>
+      </c>
+      <c r="Q2">
+        <v>5.0452</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1471111537897008</v>
+      </c>
+      <c r="T2">
+        <v>1.356705663379757</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.24</v>
+      </c>
+      <c r="W2">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1468105270206055</v>
+      </c>
+      <c r="C3">
+        <v>93.35728216316296</v>
+      </c>
+      <c r="D3">
+        <v>84.40468216316296</v>
+      </c>
+      <c r="E3">
+        <v>-8.092599999999999</v>
+      </c>
+      <c r="F3">
+        <v>0.9474000000000001</v>
+      </c>
+      <c r="G3">
+        <v>9.9</v>
+      </c>
+      <c r="H3">
+        <v>85.7</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>6.19</v>
+      </c>
+      <c r="K3">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L3">
+        <v>4.77</v>
+      </c>
+      <c r="M3">
+        <v>0.04329618000000001</v>
+      </c>
+      <c r="N3">
+        <v>4.72670382</v>
+      </c>
+      <c r="O3">
+        <v>1.1344089168</v>
+      </c>
+      <c r="P3">
+        <v>3.5922949032</v>
+      </c>
+      <c r="Q3">
+        <v>5.012294903200001</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.147942633354147</v>
+      </c>
+      <c r="T3">
+        <v>1.367120777563278</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.24</v>
+      </c>
+      <c r="W3">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>110.1713823251843</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1465099002515102</v>
+      </c>
+      <c r="C4">
+        <v>92.64546224295115</v>
+      </c>
+      <c r="D4">
+        <v>84.64026224295115</v>
+      </c>
+      <c r="E4">
+        <v>-7.145199999999999</v>
+      </c>
+      <c r="F4">
+        <v>1.8948</v>
+      </c>
+      <c r="G4">
+        <v>9.9</v>
+      </c>
+      <c r="H4">
+        <v>85.7</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>6.19</v>
+      </c>
+      <c r="K4">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L4">
+        <v>4.77</v>
+      </c>
+      <c r="M4">
+        <v>0.08659236000000002</v>
+      </c>
+      <c r="N4">
+        <v>4.68340764</v>
+      </c>
+      <c r="O4">
+        <v>1.1240178336</v>
+      </c>
+      <c r="P4">
+        <v>3.5593898064</v>
+      </c>
+      <c r="Q4">
+        <v>4.9793898064</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1487910818892961</v>
+      </c>
+      <c r="T4">
+        <v>1.377748445097484</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.24</v>
+      </c>
+      <c r="W4">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>55.08569116259216</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.146209273482415</v>
+      </c>
+      <c r="C5">
+        <v>91.93496104831955</v>
+      </c>
+      <c r="D5">
+        <v>84.87716104831955</v>
+      </c>
+      <c r="E5">
+        <v>-6.197799999999999</v>
+      </c>
+      <c r="F5">
+        <v>2.8422</v>
+      </c>
+      <c r="G5">
+        <v>9.9</v>
+      </c>
+      <c r="H5">
+        <v>85.7</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>6.19</v>
+      </c>
+      <c r="K5">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L5">
+        <v>4.77</v>
+      </c>
+      <c r="M5">
+        <v>0.12988854</v>
+      </c>
+      <c r="N5">
+        <v>4.64011146</v>
+      </c>
+      <c r="O5">
+        <v>1.1136267504</v>
+      </c>
+      <c r="P5">
+        <v>3.5264847096</v>
+      </c>
+      <c r="Q5">
+        <v>4.946484709600001</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1496570242086752</v>
+      </c>
+      <c r="T5">
+        <v>1.388595239797343</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.24</v>
+      </c>
+      <c r="W5">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>36.72379410839478</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1459086467133197</v>
+      </c>
+      <c r="C6">
+        <v>91.22578968325166</v>
+      </c>
+      <c r="D6">
+        <v>85.11538968325166</v>
+      </c>
+      <c r="E6">
+        <v>-5.250399999999999</v>
+      </c>
+      <c r="F6">
+        <v>3.789600000000001</v>
+      </c>
+      <c r="G6">
+        <v>9.9</v>
+      </c>
+      <c r="H6">
+        <v>85.7</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>6.19</v>
+      </c>
+      <c r="K6">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L6">
+        <v>4.77</v>
+      </c>
+      <c r="M6">
+        <v>0.17318472</v>
+      </c>
+      <c r="N6">
+        <v>4.59681528</v>
+      </c>
+      <c r="O6">
+        <v>1.1032356672</v>
+      </c>
+      <c r="P6">
+        <v>3.4935796128</v>
+      </c>
+      <c r="Q6">
+        <v>4.9135796128</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1505410069930413</v>
+      </c>
+      <c r="T6">
+        <v>1.399668009386783</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.24</v>
+      </c>
+      <c r="W6">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>27.54284558129608</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1456080199442244</v>
+      </c>
+      <c r="C7">
+        <v>90.51795937674586</v>
+      </c>
+      <c r="D7">
+        <v>85.35495937674585</v>
+      </c>
+      <c r="E7">
+        <v>-4.302999999999998</v>
+      </c>
+      <c r="F7">
+        <v>4.737000000000001</v>
+      </c>
+      <c r="G7">
+        <v>9.9</v>
+      </c>
+      <c r="H7">
+        <v>85.7</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>6.19</v>
+      </c>
+      <c r="K7">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L7">
+        <v>4.77</v>
+      </c>
+      <c r="M7">
+        <v>0.2164809000000001</v>
+      </c>
+      <c r="N7">
+        <v>4.5535191</v>
+      </c>
+      <c r="O7">
+        <v>1.092844584</v>
+      </c>
+      <c r="P7">
+        <v>3.460674516</v>
+      </c>
+      <c r="Q7">
+        <v>4.880674516000001</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1514435999412888</v>
+      </c>
+      <c r="T7">
+        <v>1.410973889914947</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.24</v>
+      </c>
+      <c r="W7">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>22.03427646503686</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1453073931751291</v>
+      </c>
+      <c r="C8">
+        <v>89.81148148458018</v>
+      </c>
+      <c r="D8">
+        <v>85.59588148458018</v>
+      </c>
+      <c r="E8">
+        <v>-3.355599999999999</v>
+      </c>
+      <c r="F8">
+        <v>5.6844</v>
+      </c>
+      <c r="G8">
+        <v>9.9</v>
+      </c>
+      <c r="H8">
+        <v>85.7</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>6.19</v>
+      </c>
+      <c r="K8">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L8">
+        <v>4.77</v>
+      </c>
+      <c r="M8">
+        <v>0.25977708</v>
+      </c>
+      <c r="N8">
+        <v>4.510222919999999</v>
+      </c>
+      <c r="O8">
+        <v>1.0824535008</v>
+      </c>
+      <c r="P8">
+        <v>3.4277694192</v>
+      </c>
+      <c r="Q8">
+        <v>4.8477694192</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1523653969948182</v>
+      </c>
+      <c r="T8">
+        <v>1.422520321092647</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.24</v>
+      </c>
+      <c r="W8">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>18.36189705419739</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1450067664060338</v>
+      </c>
+      <c r="C9">
+        <v>89.10636749110634</v>
+      </c>
+      <c r="D9">
+        <v>85.83816749110633</v>
+      </c>
+      <c r="E9">
+        <v>-2.408199999999998</v>
+      </c>
+      <c r="F9">
+        <v>6.631800000000001</v>
+      </c>
+      <c r="G9">
+        <v>9.9</v>
+      </c>
+      <c r="H9">
+        <v>85.7</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>6.19</v>
+      </c>
+      <c r="K9">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L9">
+        <v>4.77</v>
+      </c>
+      <c r="M9">
+        <v>0.3030732600000001</v>
+      </c>
+      <c r="N9">
+        <v>4.46692674</v>
+      </c>
+      <c r="O9">
+        <v>1.0720624176</v>
+      </c>
+      <c r="P9">
+        <v>3.3948643224</v>
+      </c>
+      <c r="Q9">
+        <v>4.814864322400001</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1533070176408966</v>
+      </c>
+      <c r="T9">
+        <v>1.434315062618255</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0.24</v>
+      </c>
+      <c r="W9">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>15.73876890359776</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1447061396369385</v>
+      </c>
+      <c r="C10">
+        <v>88.40262901107461</v>
+      </c>
+      <c r="D10">
+        <v>86.0818290110746</v>
+      </c>
+      <c r="E10">
+        <v>-1.460799999999998</v>
+      </c>
+      <c r="F10">
+        <v>7.579200000000001</v>
+      </c>
+      <c r="G10">
+        <v>9.9</v>
+      </c>
+      <c r="H10">
+        <v>85.7</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>6.19</v>
+      </c>
+      <c r="K10">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L10">
+        <v>4.77</v>
+      </c>
+      <c r="M10">
+        <v>0.3463694400000001</v>
+      </c>
+      <c r="N10">
+        <v>4.423630559999999</v>
+      </c>
+      <c r="O10">
+        <v>1.0616713344</v>
+      </c>
+      <c r="P10">
+        <v>3.3619592256</v>
+      </c>
+      <c r="Q10">
+        <v>4.781959225600001</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1542691083010201</v>
+      </c>
+      <c r="T10">
+        <v>1.446366211568332</v>
+      </c>
+      <c r="U10">
+        <v>0.0457</v>
+      </c>
+      <c r="V10">
+        <v>0.24</v>
+      </c>
+      <c r="W10">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>13.77142279064804</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1445149528678433</v>
+      </c>
+      <c r="C11">
+        <v>87.61090903854443</v>
+      </c>
+      <c r="D11">
+        <v>86.23750903854443</v>
+      </c>
+      <c r="E11">
+        <v>-0.513399999999999</v>
+      </c>
+      <c r="F11">
+        <v>8.5266</v>
+      </c>
+      <c r="G11">
+        <v>9.9</v>
+      </c>
+      <c r="H11">
+        <v>85.7</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>6.19</v>
+      </c>
+      <c r="K11">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L11">
+        <v>4.77</v>
+      </c>
+      <c r="M11">
+        <v>0.40330818</v>
+      </c>
+      <c r="N11">
+        <v>4.36669182</v>
+      </c>
+      <c r="O11">
+        <v>1.0480060368</v>
+      </c>
+      <c r="P11">
+        <v>3.3186857832</v>
+      </c>
+      <c r="Q11">
+        <v>4.738685783200001</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1552523438108168</v>
+      </c>
+      <c r="T11">
+        <v>1.458682220934895</v>
+      </c>
+      <c r="U11">
+        <v>0.0473</v>
+      </c>
+      <c r="V11">
+        <v>0.24</v>
+      </c>
+      <c r="W11">
+        <v>0.035948</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>11.82718386718563</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.144226486098748</v>
+      </c>
+      <c r="C12">
+        <v>86.89947114377738</v>
+      </c>
+      <c r="D12">
+        <v>86.47347114377737</v>
+      </c>
+      <c r="E12">
+        <v>0.4340000000000028</v>
+      </c>
+      <c r="F12">
+        <v>9.474000000000002</v>
+      </c>
+      <c r="G12">
+        <v>9.9</v>
+      </c>
+      <c r="H12">
+        <v>85.7</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>6.19</v>
+      </c>
+      <c r="K12">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L12">
+        <v>4.77</v>
+      </c>
+      <c r="M12">
+        <v>0.4481202000000001</v>
+      </c>
+      <c r="N12">
+        <v>4.3218798</v>
+      </c>
+      <c r="O12">
+        <v>1.037251152</v>
+      </c>
+      <c r="P12">
+        <v>3.284628648</v>
+      </c>
+      <c r="Q12">
+        <v>4.704628648000001</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1562574289986089</v>
+      </c>
+      <c r="T12">
+        <v>1.471271919398492</v>
+      </c>
+      <c r="U12">
+        <v>0.0473</v>
+      </c>
+      <c r="V12">
+        <v>0.24</v>
+      </c>
+      <c r="W12">
+        <v>0.035948</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>10.64446548046707</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1442556993296527</v>
+      </c>
+      <c r="C13">
+        <v>85.92811635047831</v>
+      </c>
+      <c r="D13">
+        <v>86.44951635047831</v>
+      </c>
+      <c r="E13">
+        <v>1.381400000000001</v>
+      </c>
+      <c r="F13">
+        <v>10.4214</v>
+      </c>
+      <c r="G13">
+        <v>9.9</v>
+      </c>
+      <c r="H13">
+        <v>85.7</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>6.19</v>
+      </c>
+      <c r="K13">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L13">
+        <v>4.77</v>
+      </c>
+      <c r="M13">
+        <v>0.53253354</v>
+      </c>
+      <c r="N13">
+        <v>4.237466459999999</v>
+      </c>
+      <c r="O13">
+        <v>1.0169919504</v>
+      </c>
+      <c r="P13">
+        <v>3.2204745096</v>
+      </c>
+      <c r="Q13">
+        <v>4.640474509600001</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1572851003703963</v>
+      </c>
+      <c r="T13">
+        <v>1.484144532434305</v>
+      </c>
+      <c r="U13">
+        <v>0.0511</v>
+      </c>
+      <c r="V13">
+        <v>0.24</v>
+      </c>
+      <c r="W13">
+        <v>0.038836</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>8.957182302545675</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1439961125605574</v>
+      </c>
+      <c r="C14">
+        <v>85.19404315593752</v>
+      </c>
+      <c r="D14">
+        <v>86.66284315593752</v>
+      </c>
+      <c r="E14">
+        <v>2.328800000000001</v>
+      </c>
+      <c r="F14">
+        <v>11.3688</v>
+      </c>
+      <c r="G14">
+        <v>9.9</v>
+      </c>
+      <c r="H14">
+        <v>85.7</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>6.19</v>
+      </c>
+      <c r="K14">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L14">
+        <v>4.77</v>
+      </c>
+      <c r="M14">
+        <v>0.58094568</v>
+      </c>
+      <c r="N14">
+        <v>4.189054319999999</v>
+      </c>
+      <c r="O14">
+        <v>1.0053730368</v>
+      </c>
+      <c r="P14">
+        <v>3.183681283199999</v>
+      </c>
+      <c r="Q14">
+        <v>4.6036812832</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1583361279097243</v>
+      </c>
+      <c r="T14">
+        <v>1.497309704857295</v>
+      </c>
+      <c r="U14">
+        <v>0.0511</v>
+      </c>
+      <c r="V14">
+        <v>0.24</v>
+      </c>
+      <c r="W14">
+        <v>0.038836</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>8.210750444000201</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1439242457914621</v>
+      </c>
+      <c r="C15">
+        <v>84.30588903676488</v>
+      </c>
+      <c r="D15">
+        <v>86.72208903676487</v>
+      </c>
+      <c r="E15">
+        <v>3.276200000000003</v>
+      </c>
+      <c r="F15">
+        <v>12.3162</v>
+      </c>
+      <c r="G15">
+        <v>9.9</v>
+      </c>
+      <c r="H15">
+        <v>85.7</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>6.19</v>
+      </c>
+      <c r="K15">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L15">
+        <v>4.77</v>
+      </c>
+      <c r="M15">
+        <v>0.6527586000000002</v>
+      </c>
+      <c r="N15">
+        <v>4.117241399999999</v>
+      </c>
+      <c r="O15">
+        <v>0.9881379359999998</v>
+      </c>
+      <c r="P15">
+        <v>3.129103464</v>
+      </c>
+      <c r="Q15">
+        <v>4.549103464</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1594113170016806</v>
+      </c>
+      <c r="T15">
+        <v>1.510777524922194</v>
+      </c>
+      <c r="U15">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V15">
+        <v>0.24</v>
+      </c>
+      <c r="W15">
+        <v>0.04028</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>7.307448726068102</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1436790990223668</v>
+      </c>
+      <c r="C16">
+        <v>83.5611952016226</v>
+      </c>
+      <c r="D16">
+        <v>86.92479520162259</v>
+      </c>
+      <c r="E16">
+        <v>4.223600000000003</v>
+      </c>
+      <c r="F16">
+        <v>13.2636</v>
+      </c>
+      <c r="G16">
+        <v>9.9</v>
+      </c>
+      <c r="H16">
+        <v>85.7</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>6.19</v>
+      </c>
+      <c r="K16">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L16">
+        <v>4.77</v>
+      </c>
+      <c r="M16">
+        <v>0.7029708000000002</v>
+      </c>
+      <c r="N16">
+        <v>4.067029199999999</v>
+      </c>
+      <c r="O16">
+        <v>0.9760870079999998</v>
+      </c>
+      <c r="P16">
+        <v>3.090942192</v>
+      </c>
+      <c r="Q16">
+        <v>4.510942192</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1605115104911242</v>
+      </c>
+      <c r="T16">
+        <v>1.52455855010488</v>
+      </c>
+      <c r="U16">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V16">
+        <v>0.24</v>
+      </c>
+      <c r="W16">
+        <v>0.04028</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>6.785488102777524</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1434339522532715</v>
+      </c>
+      <c r="C17">
+        <v>82.81745120657182</v>
+      </c>
+      <c r="D17">
+        <v>87.12845120657181</v>
+      </c>
+      <c r="E17">
+        <v>5.171000000000001</v>
+      </c>
+      <c r="F17">
+        <v>14.211</v>
+      </c>
+      <c r="G17">
+        <v>9.9</v>
+      </c>
+      <c r="H17">
+        <v>85.7</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>6.19</v>
+      </c>
+      <c r="K17">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L17">
+        <v>4.77</v>
+      </c>
+      <c r="M17">
+        <v>0.753183</v>
+      </c>
+      <c r="N17">
+        <v>4.016817</v>
+      </c>
+      <c r="O17">
+        <v>0.9640360799999999</v>
+      </c>
+      <c r="P17">
+        <v>3.05278092</v>
+      </c>
+      <c r="Q17">
+        <v>4.472780920000001</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1616375908862018</v>
+      </c>
+      <c r="T17">
+        <v>1.53866383470363</v>
+      </c>
+      <c r="U17">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V17">
+        <v>0.24</v>
+      </c>
+      <c r="W17">
+        <v>0.04028</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>6.333122229259024</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1434320054841763</v>
+      </c>
+      <c r="C18">
+        <v>81.871672306878</v>
+      </c>
+      <c r="D18">
+        <v>87.13007230687799</v>
+      </c>
+      <c r="E18">
+        <v>6.118400000000003</v>
+      </c>
+      <c r="F18">
+        <v>15.1584</v>
+      </c>
+      <c r="G18">
+        <v>9.9</v>
+      </c>
+      <c r="H18">
+        <v>85.7</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>6.19</v>
+      </c>
+      <c r="K18">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L18">
+        <v>4.77</v>
+      </c>
+      <c r="M18">
+        <v>0.8337120000000001</v>
+      </c>
+      <c r="N18">
+        <v>3.936287999999999</v>
+      </c>
+      <c r="O18">
+        <v>0.9447091199999998</v>
+      </c>
+      <c r="P18">
+        <v>2.99157888</v>
+      </c>
+      <c r="Q18">
+        <v>4.41157888</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1627904827192575</v>
+      </c>
+      <c r="T18">
+        <v>1.553104959411874</v>
+      </c>
+      <c r="U18">
+        <v>0.055</v>
+      </c>
+      <c r="V18">
+        <v>0.24</v>
+      </c>
+      <c r="W18">
+        <v>0.0418</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>5.721400195751049</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.143202058715081</v>
+      </c>
+      <c r="C19">
+        <v>81.11617732163143</v>
+      </c>
+      <c r="D19">
+        <v>87.32197732163142</v>
+      </c>
+      <c r="E19">
+        <v>7.065800000000003</v>
+      </c>
+      <c r="F19">
+        <v>16.1058</v>
+      </c>
+      <c r="G19">
+        <v>9.9</v>
+      </c>
+      <c r="H19">
+        <v>85.7</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>6.19</v>
+      </c>
+      <c r="K19">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L19">
+        <v>4.77</v>
+      </c>
+      <c r="M19">
+        <v>0.8858190000000001</v>
+      </c>
+      <c r="N19">
+        <v>3.884180999999999</v>
+      </c>
+      <c r="O19">
+        <v>0.9322034399999999</v>
+      </c>
+      <c r="P19">
+        <v>2.95197756</v>
+      </c>
+      <c r="Q19">
+        <v>4.37197756</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1639711550784108</v>
+      </c>
+      <c r="T19">
+        <v>1.567894063028751</v>
+      </c>
+      <c r="U19">
+        <v>0.055</v>
+      </c>
+      <c r="V19">
+        <v>0.24</v>
+      </c>
+      <c r="W19">
+        <v>0.0418</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>5.384847243059811</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1429721119459857</v>
+      </c>
+      <c r="C20">
+        <v>80.36152954850891</v>
+      </c>
+      <c r="D20">
+        <v>87.51472954850891</v>
+      </c>
+      <c r="E20">
+        <v>8.013200000000001</v>
+      </c>
+      <c r="F20">
+        <v>17.0532</v>
+      </c>
+      <c r="G20">
+        <v>9.9</v>
+      </c>
+      <c r="H20">
+        <v>85.7</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>6.19</v>
+      </c>
+      <c r="K20">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L20">
+        <v>4.77</v>
+      </c>
+      <c r="M20">
+        <v>0.937926</v>
+      </c>
+      <c r="N20">
+        <v>3.832074</v>
+      </c>
+      <c r="O20">
+        <v>0.9196977599999998</v>
+      </c>
+      <c r="P20">
+        <v>2.91237624</v>
+      </c>
+      <c r="Q20">
+        <v>4.33237624</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1651806243243728</v>
+      </c>
+      <c r="T20">
+        <v>1.583043876489941</v>
+      </c>
+      <c r="U20">
+        <v>0.055</v>
+      </c>
+      <c r="V20">
+        <v>0.24</v>
+      </c>
+      <c r="W20">
+        <v>0.0418</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>5.085689062889823</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1427421651768905</v>
+      </c>
+      <c r="C21">
+        <v>79.60773461026299</v>
+      </c>
+      <c r="D21">
+        <v>87.70833461026299</v>
+      </c>
+      <c r="E21">
+        <v>8.960600000000003</v>
+      </c>
+      <c r="F21">
+        <v>18.0006</v>
+      </c>
+      <c r="G21">
+        <v>9.9</v>
+      </c>
+      <c r="H21">
+        <v>85.7</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>6.19</v>
+      </c>
+      <c r="K21">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L21">
+        <v>4.77</v>
+      </c>
+      <c r="M21">
+        <v>0.9900330000000002</v>
+      </c>
+      <c r="N21">
+        <v>3.779966999999999</v>
+      </c>
+      <c r="O21">
+        <v>0.9071920799999997</v>
+      </c>
+      <c r="P21">
+        <v>2.872774919999999</v>
+      </c>
+      <c r="Q21">
+        <v>4.29277492</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1664199570085067</v>
+      </c>
+      <c r="T21">
+        <v>1.598567759419309</v>
+      </c>
+      <c r="U21">
+        <v>0.055</v>
+      </c>
+      <c r="V21">
+        <v>0.24</v>
+      </c>
+      <c r="W21">
+        <v>0.0418</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>4.818021217474568</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1425122184077952</v>
+      </c>
+      <c r="C22">
+        <v>78.85479817951243</v>
+      </c>
+      <c r="D22">
+        <v>87.90279817951243</v>
+      </c>
+      <c r="E22">
+        <v>9.908000000000005</v>
+      </c>
+      <c r="F22">
+        <v>18.948</v>
+      </c>
+      <c r="G22">
+        <v>9.9</v>
+      </c>
+      <c r="H22">
+        <v>85.7</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>6.19</v>
+      </c>
+      <c r="K22">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L22">
+        <v>4.77</v>
+      </c>
+      <c r="M22">
+        <v>1.04214</v>
+      </c>
+      <c r="N22">
+        <v>3.727859999999999</v>
+      </c>
+      <c r="O22">
+        <v>0.8946863999999998</v>
+      </c>
+      <c r="P22">
+        <v>2.833173599999999</v>
+      </c>
+      <c r="Q22">
+        <v>4.2531736</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.167690273009744</v>
+      </c>
+      <c r="T22">
+        <v>1.614479739421911</v>
+      </c>
+      <c r="U22">
+        <v>0.055</v>
+      </c>
+      <c r="V22">
+        <v>0.24</v>
+      </c>
+      <c r="W22">
+        <v>0.0418</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>4.577120156600839</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1428887516386999</v>
+      </c>
+      <c r="C23">
+        <v>77.58941641795784</v>
+      </c>
+      <c r="D23">
+        <v>87.58481641795782</v>
+      </c>
+      <c r="E23">
+        <v>10.8554</v>
+      </c>
+      <c r="F23">
+        <v>19.8954</v>
+      </c>
+      <c r="G23">
+        <v>9.9</v>
+      </c>
+      <c r="H23">
+        <v>85.7</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>6.19</v>
+      </c>
+      <c r="K23">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L23">
+        <v>4.77</v>
+      </c>
+      <c r="M23">
+        <v>1.16984952</v>
+      </c>
+      <c r="N23">
+        <v>3.600150479999999</v>
+      </c>
+      <c r="O23">
+        <v>0.8640361151999998</v>
+      </c>
+      <c r="P23">
+        <v>2.736114364799999</v>
+      </c>
+      <c r="Q23">
+        <v>4.156114364800001</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1689927489097467</v>
+      </c>
+      <c r="T23">
+        <v>1.630794554361288</v>
+      </c>
+      <c r="U23">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V23">
+        <v>0.24</v>
+      </c>
+      <c r="W23">
+        <v>0.04468800000000001</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>4.07744749940146</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1433899248696046</v>
+      </c>
+      <c r="C24">
+        <v>76.22232814036214</v>
+      </c>
+      <c r="D24">
+        <v>87.16512814036213</v>
+      </c>
+      <c r="E24">
+        <v>11.8028</v>
+      </c>
+      <c r="F24">
+        <v>20.8428</v>
+      </c>
+      <c r="G24">
+        <v>9.9</v>
+      </c>
+      <c r="H24">
+        <v>85.7</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>6.19</v>
+      </c>
+      <c r="K24">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L24">
+        <v>4.77</v>
+      </c>
+      <c r="M24">
+        <v>1.3130964</v>
+      </c>
+      <c r="N24">
+        <v>3.4569036</v>
+      </c>
+      <c r="O24">
+        <v>0.8296568639999998</v>
+      </c>
+      <c r="P24">
+        <v>2.627246736</v>
+      </c>
+      <c r="Q24">
+        <v>4.047246736</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1703286216276982</v>
+      </c>
+      <c r="T24">
+        <v>1.647527697888854</v>
+      </c>
+      <c r="U24">
+        <v>0.063</v>
+      </c>
+      <c r="V24">
+        <v>0.24</v>
+      </c>
+      <c r="W24">
+        <v>0.04788</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>3.632635044921301</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1444618581005093</v>
+      </c>
+      <c r="C25">
+        <v>74.3906431286331</v>
+      </c>
+      <c r="D25">
+        <v>86.28084312863309</v>
+      </c>
+      <c r="E25">
+        <v>12.7502</v>
+      </c>
+      <c r="F25">
+        <v>21.7902</v>
+      </c>
+      <c r="G25">
+        <v>9.9</v>
+      </c>
+      <c r="H25">
+        <v>85.7</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>6.19</v>
+      </c>
+      <c r="K25">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L25">
+        <v>4.77</v>
+      </c>
+      <c r="M25">
+        <v>1.52749302</v>
+      </c>
+      <c r="N25">
+        <v>3.242506979999999</v>
+      </c>
+      <c r="O25">
+        <v>0.7782016751999998</v>
+      </c>
+      <c r="P25">
+        <v>2.4643053048</v>
+      </c>
+      <c r="Q25">
+        <v>3.884305304800001</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1716991923383238</v>
+      </c>
+      <c r="T25">
+        <v>1.664695468521032</v>
+      </c>
+      <c r="U25">
+        <v>0.0701</v>
+      </c>
+      <c r="V25">
+        <v>0.24</v>
+      </c>
+      <c r="W25">
+        <v>0.053276</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>3.122763860485594</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.148231791331414</v>
+      </c>
+      <c r="C26">
+        <v>70.47086175989517</v>
+      </c>
+      <c r="D26">
+        <v>83.30846175989517</v>
+      </c>
+      <c r="E26">
+        <v>13.6976</v>
+      </c>
+      <c r="F26">
+        <v>22.7376</v>
+      </c>
+      <c r="G26">
+        <v>9.9</v>
+      </c>
+      <c r="H26">
+        <v>85.7</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>6.19</v>
+      </c>
+      <c r="K26">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L26">
+        <v>4.77</v>
+      </c>
+      <c r="M26">
+        <v>2.07821664</v>
+      </c>
+      <c r="N26">
+        <v>2.691783359999999</v>
+      </c>
+      <c r="O26">
+        <v>0.6460280063999998</v>
+      </c>
+      <c r="P26">
+        <v>2.045755353599999</v>
+      </c>
+      <c r="Q26">
+        <v>3.4657553536</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.173105830699229</v>
+      </c>
+      <c r="T26">
+        <v>1.682315022590899</v>
+      </c>
+      <c r="U26">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V26">
+        <v>0.24</v>
+      </c>
+      <c r="W26">
+        <v>0.06946400000000001</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>2.295237131774673</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1482784845623187</v>
+      </c>
+      <c r="C27">
+        <v>69.4879302008238</v>
+      </c>
+      <c r="D27">
+        <v>83.27293020082379</v>
+      </c>
+      <c r="E27">
+        <v>14.645</v>
+      </c>
+      <c r="F27">
+        <v>23.685</v>
+      </c>
+      <c r="G27">
+        <v>9.9</v>
+      </c>
+      <c r="H27">
+        <v>85.7</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>6.19</v>
+      </c>
+      <c r="K27">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L27">
+        <v>4.77</v>
+      </c>
+      <c r="M27">
+        <v>2.164809</v>
+      </c>
+      <c r="N27">
+        <v>2.605190999999999</v>
+      </c>
+      <c r="O27">
+        <v>0.6252458399999997</v>
+      </c>
+      <c r="P27">
+        <v>1.979945159999999</v>
+      </c>
+      <c r="Q27">
+        <v>3.39994516</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.174549979416425</v>
+      </c>
+      <c r="T27">
+        <v>1.700404431435962</v>
+      </c>
+      <c r="U27">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V27">
+        <v>0.24</v>
+      </c>
+      <c r="W27">
+        <v>0.06946400000000001</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>2.203427646503687</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1483251777932235</v>
+      </c>
+      <c r="C28">
+        <v>68.50502893767752</v>
+      </c>
+      <c r="D28">
+        <v>83.23742893767752</v>
+      </c>
+      <c r="E28">
+        <v>15.5924</v>
+      </c>
+      <c r="F28">
+        <v>24.6324</v>
+      </c>
+      <c r="G28">
+        <v>9.9</v>
+      </c>
+      <c r="H28">
+        <v>85.7</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>6.19</v>
+      </c>
+      <c r="K28">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L28">
+        <v>4.77</v>
+      </c>
+      <c r="M28">
+        <v>2.25140136</v>
+      </c>
+      <c r="N28">
+        <v>2.518598639999999</v>
+      </c>
+      <c r="O28">
+        <v>0.6044636735999998</v>
+      </c>
+      <c r="P28">
+        <v>1.914134966399999</v>
+      </c>
+      <c r="Q28">
+        <v>3.3341349664</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1760331591800317</v>
+      </c>
+      <c r="T28">
+        <v>1.718982743222784</v>
+      </c>
+      <c r="U28">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V28">
+        <v>0.24</v>
+      </c>
+      <c r="W28">
+        <v>0.06946400000000001</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>2.118680429330468</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1483718710241282</v>
+      </c>
+      <c r="C29">
+        <v>67.52215793172522</v>
+      </c>
+      <c r="D29">
+        <v>83.20195793172522</v>
+      </c>
+      <c r="E29">
+        <v>16.53980000000001</v>
+      </c>
+      <c r="F29">
+        <v>25.57980000000001</v>
+      </c>
+      <c r="G29">
+        <v>9.9</v>
+      </c>
+      <c r="H29">
+        <v>85.7</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>6.19</v>
+      </c>
+      <c r="K29">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L29">
+        <v>4.77</v>
+      </c>
+      <c r="M29">
+        <v>2.337993720000001</v>
+      </c>
+      <c r="N29">
+        <v>2.432006279999999</v>
+      </c>
+      <c r="O29">
+        <v>0.5836815071999997</v>
+      </c>
+      <c r="P29">
+        <v>1.848324772799999</v>
+      </c>
+      <c r="Q29">
+        <v>3.2683247728</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.177556974005655</v>
+      </c>
+      <c r="T29">
+        <v>1.73807004985308</v>
+      </c>
+      <c r="U29">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V29">
+        <v>0.24</v>
+      </c>
+      <c r="W29">
+        <v>0.06946400000000001</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>2.040210783799709</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1529086442550329</v>
+      </c>
+      <c r="C30">
+        <v>63.26678404448958</v>
+      </c>
+      <c r="D30">
+        <v>79.89398404448959</v>
+      </c>
+      <c r="E30">
+        <v>17.4872</v>
+      </c>
+      <c r="F30">
+        <v>26.5272</v>
+      </c>
+      <c r="G30">
+        <v>9.9</v>
+      </c>
+      <c r="H30">
+        <v>85.7</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>6.19</v>
+      </c>
+      <c r="K30">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L30">
+        <v>4.77</v>
+      </c>
+      <c r="M30">
+        <v>2.984310000000001</v>
+      </c>
+      <c r="N30">
+        <v>1.785689999999999</v>
+      </c>
+      <c r="O30">
+        <v>0.4285655999999997</v>
+      </c>
+      <c r="P30">
+        <v>1.357124399999999</v>
+      </c>
+      <c r="Q30">
+        <v>2.7771244</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.179123117020879</v>
+      </c>
+      <c r="T30">
+        <v>1.75768755944533</v>
+      </c>
+      <c r="U30">
+        <v>0.1125</v>
+      </c>
+      <c r="V30">
+        <v>0.24</v>
+      </c>
+      <c r="W30">
+        <v>0.08550000000000001</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>1.598359419765373</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1531156974859376</v>
+      </c>
+      <c r="C31">
+        <v>62.17467681801003</v>
+      </c>
+      <c r="D31">
+        <v>79.74927681801003</v>
+      </c>
+      <c r="E31">
+        <v>18.4346</v>
+      </c>
+      <c r="F31">
+        <v>27.4746</v>
+      </c>
+      <c r="G31">
+        <v>9.9</v>
+      </c>
+      <c r="H31">
+        <v>85.7</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>6.19</v>
+      </c>
+      <c r="K31">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L31">
+        <v>4.77</v>
+      </c>
+      <c r="M31">
+        <v>3.0908925</v>
+      </c>
+      <c r="N31">
+        <v>1.679107499999999</v>
+      </c>
+      <c r="O31">
+        <v>0.4029857999999998</v>
+      </c>
+      <c r="P31">
+        <v>1.2761217</v>
+      </c>
+      <c r="Q31">
+        <v>2.6961217</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1807333767407572</v>
+      </c>
+      <c r="T31">
+        <v>1.777857674941586</v>
+      </c>
+      <c r="U31">
+        <v>0.1125</v>
+      </c>
+      <c r="V31">
+        <v>0.24</v>
+      </c>
+      <c r="W31">
+        <v>0.08550000000000001</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>1.543243577704498</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1757104438798544</v>
+      </c>
+      <c r="C32">
+        <v>48.0660114408963</v>
+      </c>
+      <c r="D32">
+        <v>66.5880114408963</v>
+      </c>
+      <c r="E32">
+        <v>19.382</v>
+      </c>
+      <c r="F32">
+        <v>28.422</v>
+      </c>
+      <c r="G32">
+        <v>9.9</v>
+      </c>
+      <c r="H32">
+        <v>85.7</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>6.19</v>
+      </c>
+      <c r="K32">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L32">
+        <v>4.77</v>
+      </c>
+      <c r="M32">
+        <v>5.5877652</v>
+      </c>
+      <c r="N32">
+        <v>-0.8177652000000002</v>
+      </c>
+      <c r="O32">
+        <v>-0.196263648</v>
+      </c>
+      <c r="P32">
+        <v>-0.6215015520000001</v>
+      </c>
+      <c r="Q32">
+        <v>0.7984984480000007</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1840200587046866</v>
+      </c>
+      <c r="T32">
+        <v>1.819026657804135</v>
+      </c>
+      <c r="U32">
+        <v>0.1966</v>
+      </c>
+      <c r="V32">
+        <v>0.2048761819841678</v>
+      </c>
+      <c r="W32">
+        <v>0.1563213426219126</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.8536507582673659</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1772884438798544</v>
+      </c>
+      <c r="C33">
+        <v>46.35987750534214</v>
+      </c>
+      <c r="D33">
+        <v>65.82927750534213</v>
+      </c>
+      <c r="E33">
+        <v>20.3294</v>
+      </c>
+      <c r="F33">
+        <v>29.3694</v>
+      </c>
+      <c r="G33">
+        <v>9.9</v>
+      </c>
+      <c r="H33">
+        <v>85.7</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>6.19</v>
+      </c>
+      <c r="K33">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L33">
+        <v>4.77</v>
+      </c>
+      <c r="M33">
+        <v>5.77402404</v>
+      </c>
+      <c r="N33">
+        <v>-1.004024040000001</v>
+      </c>
+      <c r="O33">
+        <v>-0.2409657696000002</v>
+      </c>
+      <c r="P33">
+        <v>-0.7630582704000006</v>
+      </c>
+      <c r="Q33">
+        <v>0.6569417296000002</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1861246972366386</v>
+      </c>
+      <c r="T33">
+        <v>1.845389362989702</v>
+      </c>
+      <c r="U33">
+        <v>0.1966</v>
+      </c>
+      <c r="V33">
+        <v>0.1982672728879043</v>
+      </c>
+      <c r="W33">
+        <v>0.157620654150238</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.8261136370329347</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1788664438798544</v>
+      </c>
+      <c r="C34">
+        <v>44.67083948679904</v>
+      </c>
+      <c r="D34">
+        <v>65.08763948679903</v>
+      </c>
+      <c r="E34">
+        <v>21.27680000000001</v>
+      </c>
+      <c r="F34">
+        <v>30.3168</v>
+      </c>
+      <c r="G34">
+        <v>9.9</v>
+      </c>
+      <c r="H34">
+        <v>85.7</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>6.19</v>
+      </c>
+      <c r="K34">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L34">
+        <v>4.77</v>
+      </c>
+      <c r="M34">
+        <v>5.960282880000001</v>
+      </c>
+      <c r="N34">
+        <v>-1.190282880000002</v>
+      </c>
+      <c r="O34">
+        <v>-0.2856678912000004</v>
+      </c>
+      <c r="P34">
+        <v>-0.9046149888000012</v>
+      </c>
+      <c r="Q34">
+        <v>0.5153850111999996</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1882912369018833</v>
+      </c>
+      <c r="T34">
+        <v>1.872527441857198</v>
+      </c>
+      <c r="U34">
+        <v>0.1966</v>
+      </c>
+      <c r="V34">
+        <v>0.1920714206101573</v>
+      </c>
+      <c r="W34">
+        <v>0.1588387587080431</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.8002975858756554</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1866560020574897</v>
+      </c>
+      <c r="C35">
+        <v>40.29440077770262</v>
+      </c>
+      <c r="D35">
+        <v>61.65860077770262</v>
+      </c>
+      <c r="E35">
+        <v>22.22420000000001</v>
+      </c>
+      <c r="F35">
+        <v>31.26420000000001</v>
+      </c>
+      <c r="G35">
+        <v>9.9</v>
+      </c>
+      <c r="H35">
+        <v>85.7</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>6.19</v>
+      </c>
+      <c r="K35">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L35">
+        <v>4.77</v>
+      </c>
+      <c r="M35">
+        <v>6.684285960000001</v>
+      </c>
+      <c r="N35">
+        <v>-1.914285960000002</v>
+      </c>
+      <c r="O35">
+        <v>-0.4594286304000004</v>
+      </c>
+      <c r="P35">
+        <v>-1.454857329600001</v>
+      </c>
+      <c r="Q35">
+        <v>-0.03485732960000054</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1913217899565909</v>
+      </c>
+      <c r="T35">
+        <v>1.910488153645735</v>
+      </c>
+      <c r="U35">
+        <v>0.2138</v>
+      </c>
+      <c r="V35">
+        <v>0.1712673585257564</v>
+      </c>
+      <c r="W35">
+        <v>0.1771830387471933</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.7136139938573183</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1884060020574897</v>
+      </c>
+      <c r="C36">
+        <v>38.62575597550868</v>
+      </c>
+      <c r="D36">
+        <v>60.93735597550868</v>
+      </c>
+      <c r="E36">
+        <v>23.17160000000001</v>
+      </c>
+      <c r="F36">
+        <v>32.2116</v>
+      </c>
+      <c r="G36">
+        <v>9.9</v>
+      </c>
+      <c r="H36">
+        <v>85.7</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>6.19</v>
+      </c>
+      <c r="K36">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L36">
+        <v>4.77</v>
+      </c>
+      <c r="M36">
+        <v>6.886840080000001</v>
+      </c>
+      <c r="N36">
+        <v>-2.116840080000001</v>
+      </c>
+      <c r="O36">
+        <v>-0.5080416192000002</v>
+      </c>
+      <c r="P36">
+        <v>-1.608798460800001</v>
+      </c>
+      <c r="Q36">
+        <v>-0.1887984608000002</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1936327261680544</v>
+      </c>
+      <c r="T36">
+        <v>1.939434943852488</v>
+      </c>
+      <c r="U36">
+        <v>0.2138</v>
+      </c>
+      <c r="V36">
+        <v>0.1662300832749989</v>
+      </c>
+      <c r="W36">
+        <v>0.1782600081958052</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.6926253469791619</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1901560020574897</v>
+      </c>
+      <c r="C37">
+        <v>36.97378944687749</v>
+      </c>
+      <c r="D37">
+        <v>60.2327894468775</v>
+      </c>
+      <c r="E37">
+        <v>24.11900000000001</v>
+      </c>
+      <c r="F37">
+        <v>33.15900000000001</v>
+      </c>
+      <c r="G37">
+        <v>9.9</v>
+      </c>
+      <c r="H37">
+        <v>85.7</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>6.19</v>
+      </c>
+      <c r="K37">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L37">
+        <v>4.77</v>
+      </c>
+      <c r="M37">
+        <v>7.089394200000001</v>
+      </c>
+      <c r="N37">
+        <v>-2.319394200000001</v>
+      </c>
+      <c r="O37">
+        <v>-0.5566546080000003</v>
+      </c>
+      <c r="P37">
+        <v>-1.762739592000001</v>
+      </c>
+      <c r="Q37">
+        <v>-0.3427395920000003</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1960147681091014</v>
+      </c>
+      <c r="T37">
+        <v>1.969272404527142</v>
+      </c>
+      <c r="U37">
+        <v>0.2138</v>
+      </c>
+      <c r="V37">
+        <v>0.1614806523242846</v>
+      </c>
+      <c r="W37">
+        <v>0.1792754365330679</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.6728360513511857</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1919060020574897</v>
+      </c>
+      <c r="C38">
+        <v>35.33792929433262</v>
+      </c>
+      <c r="D38">
+        <v>59.54432929433262</v>
+      </c>
+      <c r="E38">
+        <v>25.0664</v>
+      </c>
+      <c r="F38">
+        <v>34.1064</v>
+      </c>
+      <c r="G38">
+        <v>9.9</v>
+      </c>
+      <c r="H38">
+        <v>85.7</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>6.19</v>
+      </c>
+      <c r="K38">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L38">
+        <v>4.77</v>
+      </c>
+      <c r="M38">
+        <v>7.291948319999999</v>
+      </c>
+      <c r="N38">
+        <v>-2.52194832</v>
+      </c>
+      <c r="O38">
+        <v>-0.6052675968</v>
+      </c>
+      <c r="P38">
+        <v>-1.9166807232</v>
+      </c>
+      <c r="Q38">
+        <v>-0.496680723199999</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1984712488608061</v>
+      </c>
+      <c r="T38">
+        <v>2.000042285847878</v>
+      </c>
+      <c r="U38">
+        <v>0.2138</v>
+      </c>
+      <c r="V38">
+        <v>0.15699507864861</v>
+      </c>
+      <c r="W38">
+        <v>0.1802344521849271</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.6541461610358752</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1936560020574897</v>
+      </c>
+      <c r="C39">
+        <v>33.71762947204225</v>
+      </c>
+      <c r="D39">
+        <v>58.87142947204225</v>
+      </c>
+      <c r="E39">
+        <v>26.0138</v>
+      </c>
+      <c r="F39">
+        <v>35.0538</v>
+      </c>
+      <c r="G39">
+        <v>9.9</v>
+      </c>
+      <c r="H39">
+        <v>85.7</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>6.19</v>
+      </c>
+      <c r="K39">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L39">
+        <v>4.77</v>
+      </c>
+      <c r="M39">
+        <v>7.49450244</v>
+      </c>
+      <c r="N39">
+        <v>-2.72450244</v>
+      </c>
+      <c r="O39">
+        <v>-0.6538805856000001</v>
+      </c>
+      <c r="P39">
+        <v>-2.0706218544</v>
+      </c>
+      <c r="Q39">
+        <v>-0.6506218543999993</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.201005713128438</v>
+      </c>
+      <c r="T39">
+        <v>2.031788988797844</v>
+      </c>
+      <c r="U39">
+        <v>0.2138</v>
+      </c>
+      <c r="V39">
+        <v>0.1527519684148638</v>
+      </c>
+      <c r="W39">
+        <v>0.1811416291529021</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.6364665350619326</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1954060020574897</v>
+      </c>
+      <c r="C40">
+        <v>32.11236834141805</v>
+      </c>
+      <c r="D40">
+        <v>58.21356834141806</v>
+      </c>
+      <c r="E40">
+        <v>26.96120000000001</v>
+      </c>
+      <c r="F40">
+        <v>36.0012</v>
+      </c>
+      <c r="G40">
+        <v>9.9</v>
+      </c>
+      <c r="H40">
+        <v>85.7</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>6.19</v>
+      </c>
+      <c r="K40">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L40">
+        <v>4.77</v>
+      </c>
+      <c r="M40">
+        <v>7.697056560000001</v>
+      </c>
+      <c r="N40">
+        <v>-2.927056560000001</v>
+      </c>
+      <c r="O40">
+        <v>-0.7024935744000003</v>
+      </c>
+      <c r="P40">
+        <v>-2.224562985600001</v>
+      </c>
+      <c r="Q40">
+        <v>-0.8045629856000005</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.2036219343079289</v>
+      </c>
+      <c r="T40">
+        <v>2.064559778939745</v>
+      </c>
+      <c r="U40">
+        <v>0.2138</v>
+      </c>
+      <c r="V40">
+        <v>0.1487321797723674</v>
+      </c>
+      <c r="W40">
+        <v>0.1820010599646678</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.6197174157181975</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1971560020574897</v>
+      </c>
+      <c r="C41">
+        <v>30.52164732248695</v>
+      </c>
+      <c r="D41">
+        <v>57.57024732248696</v>
+      </c>
+      <c r="E41">
+        <v>27.90860000000001</v>
+      </c>
+      <c r="F41">
+        <v>36.94860000000001</v>
+      </c>
+      <c r="G41">
+        <v>9.9</v>
+      </c>
+      <c r="H41">
+        <v>85.7</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>6.19</v>
+      </c>
+      <c r="K41">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L41">
+        <v>4.77</v>
+      </c>
+      <c r="M41">
+        <v>7.899610680000001</v>
+      </c>
+      <c r="N41">
+        <v>-3.129610680000002</v>
+      </c>
+      <c r="O41">
+        <v>-0.7511065632000004</v>
+      </c>
+      <c r="P41">
+        <v>-2.378504116800001</v>
+      </c>
+      <c r="Q41">
+        <v>-0.9585041168000004</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.2063239332310097</v>
+      </c>
+      <c r="T41">
+        <v>2.098405021217446</v>
+      </c>
+      <c r="U41">
+        <v>0.2138</v>
+      </c>
+      <c r="V41">
+        <v>0.1449185341371785</v>
+      </c>
+      <c r="W41">
+        <v>0.1828164174014712</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.6038272255715771</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1989060020574897</v>
+      </c>
+      <c r="C42">
+        <v>28.94498963370787</v>
+      </c>
+      <c r="D42">
+        <v>56.94098963370788</v>
+      </c>
+      <c r="E42">
+        <v>28.85600000000001</v>
+      </c>
+      <c r="F42">
+        <v>37.89600000000001</v>
+      </c>
+      <c r="G42">
+        <v>9.9</v>
+      </c>
+      <c r="H42">
+        <v>85.7</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>6.19</v>
+      </c>
+      <c r="K42">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L42">
+        <v>4.77</v>
+      </c>
+      <c r="M42">
+        <v>8.102164800000001</v>
+      </c>
+      <c r="N42">
+        <v>-3.332164800000001</v>
+      </c>
+      <c r="O42">
+        <v>-0.7997195520000002</v>
+      </c>
+      <c r="P42">
+        <v>-2.532445248000001</v>
+      </c>
+      <c r="Q42">
+        <v>-1.112445248</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.2091159987848599</v>
+      </c>
+      <c r="T42">
+        <v>2.133378438237737</v>
+      </c>
+      <c r="U42">
+        <v>0.2138</v>
+      </c>
+      <c r="V42">
+        <v>0.141295570783749</v>
+      </c>
+      <c r="W42">
+        <v>0.1835910069664345</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.5887315449322876</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.2006560020574897</v>
+      </c>
+      <c r="C43">
+        <v>27.38193911353999</v>
+      </c>
+      <c r="D43">
+        <v>56.32533911354</v>
+      </c>
+      <c r="E43">
+        <v>29.80340000000001</v>
+      </c>
+      <c r="F43">
+        <v>38.84340000000001</v>
+      </c>
+      <c r="G43">
+        <v>9.9</v>
+      </c>
+      <c r="H43">
+        <v>85.7</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>6.19</v>
+      </c>
+      <c r="K43">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L43">
+        <v>4.77</v>
+      </c>
+      <c r="M43">
+        <v>8.304718920000001</v>
+      </c>
+      <c r="N43">
+        <v>-3.534718920000001</v>
+      </c>
+      <c r="O43">
+        <v>-0.8483325408000003</v>
+      </c>
+      <c r="P43">
+        <v>-2.686386379200001</v>
+      </c>
+      <c r="Q43">
+        <v>-1.2663863792</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.212002710628671</v>
+      </c>
+      <c r="T43">
+        <v>2.169537394818037</v>
+      </c>
+      <c r="U43">
+        <v>0.2138</v>
+      </c>
+      <c r="V43">
+        <v>0.137849337349999</v>
+      </c>
+      <c r="W43">
+        <v>0.1843278116745702</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.5743722389583295</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.2024060020574897</v>
+      </c>
+      <c r="C44">
+        <v>25.83205911764071</v>
+      </c>
+      <c r="D44">
+        <v>55.72285911764071</v>
+      </c>
+      <c r="E44">
+        <v>30.75080000000001</v>
+      </c>
+      <c r="F44">
+        <v>39.7908</v>
+      </c>
+      <c r="G44">
+        <v>9.9</v>
+      </c>
+      <c r="H44">
+        <v>85.7</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>6.19</v>
+      </c>
+      <c r="K44">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L44">
+        <v>4.77</v>
+      </c>
+      <c r="M44">
+        <v>8.507273040000001</v>
+      </c>
+      <c r="N44">
+        <v>-3.737273040000002</v>
+      </c>
+      <c r="O44">
+        <v>-0.8969455296000004</v>
+      </c>
+      <c r="P44">
+        <v>-2.840327510400001</v>
+      </c>
+      <c r="Q44">
+        <v>-1.4203275104</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.2149889642601999</v>
+      </c>
+      <c r="T44">
+        <v>2.206943211970072</v>
+      </c>
+      <c r="U44">
+        <v>0.2138</v>
+      </c>
+      <c r="V44">
+        <v>0.1345672102702372</v>
+      </c>
+      <c r="W44">
+        <v>0.1850295304442233</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.5606967094593216</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.2041560020574897</v>
+      </c>
+      <c r="C45">
+        <v>24.29493148609113</v>
+      </c>
+      <c r="D45">
+        <v>55.13313148609113</v>
+      </c>
+      <c r="E45">
+        <v>31.69820000000001</v>
+      </c>
+      <c r="F45">
+        <v>40.73820000000001</v>
+      </c>
+      <c r="G45">
+        <v>9.9</v>
+      </c>
+      <c r="H45">
+        <v>85.7</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>6.19</v>
+      </c>
+      <c r="K45">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L45">
+        <v>4.77</v>
+      </c>
+      <c r="M45">
+        <v>8.709827160000001</v>
+      </c>
+      <c r="N45">
+        <v>-3.939827160000002</v>
+      </c>
+      <c r="O45">
+        <v>-0.9455585184000004</v>
+      </c>
+      <c r="P45">
+        <v>-2.994268641600002</v>
+      </c>
+      <c r="Q45">
+        <v>-1.574268641600001</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.2180799987209051</v>
+      </c>
+      <c r="T45">
+        <v>2.245661513934459</v>
+      </c>
+      <c r="U45">
+        <v>0.2138</v>
+      </c>
+      <c r="V45">
+        <v>0.1314377402639526</v>
+      </c>
+      <c r="W45">
+        <v>0.1856986111315669</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.5476572510998023</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.2059060020574897</v>
+      </c>
+      <c r="C46">
+        <v>22.77015557551511</v>
+      </c>
+      <c r="D46">
+        <v>54.55575557551511</v>
+      </c>
+      <c r="E46">
+        <v>32.6456</v>
+      </c>
+      <c r="F46">
+        <v>41.6856</v>
+      </c>
+      <c r="G46">
+        <v>9.9</v>
+      </c>
+      <c r="H46">
+        <v>85.7</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>6.19</v>
+      </c>
+      <c r="K46">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L46">
+        <v>4.77</v>
+      </c>
+      <c r="M46">
+        <v>8.91238128</v>
+      </c>
+      <c r="N46">
+        <v>-4.14238128</v>
+      </c>
+      <c r="O46">
+        <v>-0.9941715072</v>
+      </c>
+      <c r="P46">
+        <v>-3.1482097728</v>
+      </c>
+      <c r="Q46">
+        <v>-1.7282097728</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.2212814272694927</v>
+      </c>
+      <c r="T46">
+        <v>2.285762612397575</v>
+      </c>
+      <c r="U46">
+        <v>0.2138</v>
+      </c>
+      <c r="V46">
+        <v>0.1284505188943173</v>
+      </c>
+      <c r="W46">
+        <v>0.186337279060395</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.5352104953929888</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.2076560020574897</v>
+      </c>
+      <c r="C47">
+        <v>21.25734735138431</v>
+      </c>
+      <c r="D47">
+        <v>53.99034735138432</v>
+      </c>
+      <c r="E47">
+        <v>33.593</v>
+      </c>
+      <c r="F47">
+        <v>42.633</v>
+      </c>
+      <c r="G47">
+        <v>9.9</v>
+      </c>
+      <c r="H47">
+        <v>85.7</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>6.19</v>
+      </c>
+      <c r="K47">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L47">
+        <v>4.77</v>
+      </c>
+      <c r="M47">
+        <v>9.1149354</v>
+      </c>
+      <c r="N47">
+        <v>-4.344935400000001</v>
+      </c>
+      <c r="O47">
+        <v>-1.042784496</v>
+      </c>
+      <c r="P47">
+        <v>-3.302150904</v>
+      </c>
+      <c r="Q47">
+        <v>-1.882150904</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.2245992714016653</v>
+      </c>
+      <c r="T47">
+        <v>2.327321932622985</v>
+      </c>
+      <c r="U47">
+        <v>0.2138</v>
+      </c>
+      <c r="V47">
+        <v>0.125596062918888</v>
+      </c>
+      <c r="W47">
+        <v>0.1869475617479417</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.5233169288287001</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.2094060020574897</v>
+      </c>
+      <c r="C48">
+        <v>19.7561385361875</v>
+      </c>
+      <c r="D48">
+        <v>53.43653853618751</v>
+      </c>
+      <c r="E48">
+        <v>34.54040000000001</v>
+      </c>
+      <c r="F48">
+        <v>43.5804</v>
+      </c>
+      <c r="G48">
+        <v>9.9</v>
+      </c>
+      <c r="H48">
+        <v>85.7</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>6.19</v>
+      </c>
+      <c r="K48">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L48">
+        <v>4.77</v>
+      </c>
+      <c r="M48">
+        <v>9.317489520000001</v>
+      </c>
+      <c r="N48">
+        <v>-4.547489520000001</v>
+      </c>
+      <c r="O48">
+        <v>-1.0913974848</v>
+      </c>
+      <c r="P48">
+        <v>-3.456092035200001</v>
+      </c>
+      <c r="Q48">
+        <v>-2.0360920352</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.2280399986498443</v>
+      </c>
+      <c r="T48">
+        <v>2.370420486930819</v>
+      </c>
+      <c r="U48">
+        <v>0.2138</v>
+      </c>
+      <c r="V48">
+        <v>0.1228657137249992</v>
+      </c>
+      <c r="W48">
+        <v>0.1875313104055952</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.5119404738541632</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.2111560020574897</v>
+      </c>
+      <c r="C49">
+        <v>18.26617580949384</v>
+      </c>
+      <c r="D49">
+        <v>52.89397580949385</v>
+      </c>
+      <c r="E49">
+        <v>35.48780000000001</v>
+      </c>
+      <c r="F49">
+        <v>44.52780000000001</v>
+      </c>
+      <c r="G49">
+        <v>9.9</v>
+      </c>
+      <c r="H49">
+        <v>85.7</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>6.19</v>
+      </c>
+      <c r="K49">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L49">
+        <v>4.77</v>
+      </c>
+      <c r="M49">
+        <v>9.520043640000001</v>
+      </c>
+      <c r="N49">
+        <v>-4.750043640000001</v>
+      </c>
+      <c r="O49">
+        <v>-1.1400104736</v>
+      </c>
+      <c r="P49">
+        <v>-3.610033166400001</v>
+      </c>
+      <c r="Q49">
+        <v>-2.1900331664</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.2316105646621055</v>
+      </c>
+      <c r="T49">
+        <v>2.41514540177857</v>
+      </c>
+      <c r="U49">
+        <v>0.2138</v>
+      </c>
+      <c r="V49">
+        <v>0.1202515496031906</v>
+      </c>
+      <c r="W49">
+        <v>0.1880902186948378</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.5010481233466277</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.2255468683178315</v>
+      </c>
+      <c r="C50">
+        <v>13.24272281482365</v>
+      </c>
+      <c r="D50">
+        <v>48.81792281482365</v>
+      </c>
+      <c r="E50">
+        <v>36.4352</v>
+      </c>
+      <c r="F50">
+        <v>45.4752</v>
+      </c>
+      <c r="G50">
+        <v>9.9</v>
+      </c>
+      <c r="H50">
+        <v>85.7</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>6.19</v>
+      </c>
+      <c r="K50">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L50">
+        <v>4.77</v>
+      </c>
+      <c r="M50">
+        <v>10.85947776</v>
+      </c>
+      <c r="N50">
+        <v>-6.089477760000001</v>
+      </c>
+      <c r="O50">
+        <v>-1.4614746624</v>
+      </c>
+      <c r="P50">
+        <v>-4.628003097600001</v>
+      </c>
+      <c r="Q50">
+        <v>-3.2080030976</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.2365508952524187</v>
+      </c>
+      <c r="T50">
+        <v>2.477027989640758</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.1054194340925654</v>
+      </c>
+      <c r="W50">
+        <v>0.2136258391386954</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.4392476420523559</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.2275468683178315</v>
+      </c>
+      <c r="C51">
+        <v>11.7780382288604</v>
+      </c>
+      <c r="D51">
+        <v>48.3006382288604</v>
+      </c>
+      <c r="E51">
+        <v>37.3826</v>
+      </c>
+      <c r="F51">
+        <v>46.4226</v>
+      </c>
+      <c r="G51">
+        <v>9.9</v>
+      </c>
+      <c r="H51">
+        <v>85.7</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>6.19</v>
+      </c>
+      <c r="K51">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L51">
+        <v>4.77</v>
+      </c>
+      <c r="M51">
+        <v>11.08571688</v>
+      </c>
+      <c r="N51">
+        <v>-6.315716880000002</v>
+      </c>
+      <c r="O51">
+        <v>-1.5157720512</v>
+      </c>
+      <c r="P51">
+        <v>-4.799944828800001</v>
+      </c>
+      <c r="Q51">
+        <v>-3.3799448288</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.2404283637867798</v>
+      </c>
+      <c r="T51">
+        <v>2.525597165908224</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.1032680170702681</v>
+      </c>
+      <c r="W51">
+        <v>0.21413959752362</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.4302834044594506</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.2295468683178315</v>
+      </c>
+      <c r="C52">
+        <v>10.32420120418139</v>
+      </c>
+      <c r="D52">
+        <v>47.7942012041814</v>
+      </c>
+      <c r="E52">
+        <v>38.33000000000001</v>
+      </c>
+      <c r="F52">
+        <v>47.37</v>
+      </c>
+      <c r="G52">
+        <v>9.9</v>
+      </c>
+      <c r="H52">
+        <v>85.7</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>6.19</v>
+      </c>
+      <c r="K52">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L52">
+        <v>4.77</v>
+      </c>
+      <c r="M52">
+        <v>11.311956</v>
+      </c>
+      <c r="N52">
+        <v>-6.541956000000003</v>
+      </c>
+      <c r="O52">
+        <v>-1.570069440000001</v>
+      </c>
+      <c r="P52">
+        <v>-4.971886560000002</v>
+      </c>
+      <c r="Q52">
+        <v>-3.551886560000001</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.2444609310625155</v>
+      </c>
+      <c r="T52">
+        <v>2.576109109226389</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.1012026567288628</v>
+      </c>
+      <c r="W52">
+        <v>0.2146328055731476</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.4216777363702616</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.2315468683178315</v>
+      </c>
+      <c r="C53">
+        <v>8.880874068022997</v>
+      </c>
+      <c r="D53">
+        <v>47.29827406802301</v>
+      </c>
+      <c r="E53">
+        <v>39.27740000000001</v>
+      </c>
+      <c r="F53">
+        <v>48.31740000000001</v>
+      </c>
+      <c r="G53">
+        <v>9.9</v>
+      </c>
+      <c r="H53">
+        <v>85.7</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>6.19</v>
+      </c>
+      <c r="K53">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L53">
+        <v>4.77</v>
+      </c>
+      <c r="M53">
+        <v>11.53819512</v>
+      </c>
+      <c r="N53">
+        <v>-6.768195120000003</v>
+      </c>
+      <c r="O53">
+        <v>-1.624366828800001</v>
+      </c>
+      <c r="P53">
+        <v>-5.143828291200003</v>
+      </c>
+      <c r="Q53">
+        <v>-3.723828291200002</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.2486580929209341</v>
+      </c>
+      <c r="T53">
+        <v>2.628682764516723</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.09921829091064978</v>
+      </c>
+      <c r="W53">
+        <v>0.2151066721305368</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.4134095454610407</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.2335468683178315</v>
+      </c>
+      <c r="C54">
+        <v>7.447733018869577</v>
+      </c>
+      <c r="D54">
+        <v>46.81253301886959</v>
+      </c>
+      <c r="E54">
+        <v>40.22480000000001</v>
+      </c>
+      <c r="F54">
+        <v>49.26480000000001</v>
+      </c>
+      <c r="G54">
+        <v>9.9</v>
+      </c>
+      <c r="H54">
+        <v>85.7</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>6.19</v>
+      </c>
+      <c r="K54">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L54">
+        <v>4.77</v>
+      </c>
+      <c r="M54">
+        <v>11.76443424</v>
+      </c>
+      <c r="N54">
+        <v>-6.994434240000002</v>
+      </c>
+      <c r="O54">
+        <v>-1.6786642176</v>
+      </c>
+      <c r="P54">
+        <v>-5.315770022400002</v>
+      </c>
+      <c r="Q54">
+        <v>-3.895770022400001</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.2530301365234536</v>
+      </c>
+      <c r="T54">
+        <v>2.683446988777488</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.09731024685467575</v>
+      </c>
+      <c r="W54">
+        <v>0.2155623130511035</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.4054593618944823</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.2355468683178315</v>
+      </c>
+      <c r="C55">
+        <v>6.024467421423346</v>
+      </c>
+      <c r="D55">
+        <v>46.33666742142336</v>
+      </c>
+      <c r="E55">
+        <v>41.17220000000001</v>
+      </c>
+      <c r="F55">
+        <v>50.21220000000001</v>
+      </c>
+      <c r="G55">
+        <v>9.9</v>
+      </c>
+      <c r="H55">
+        <v>85.7</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>6.19</v>
+      </c>
+      <c r="K55">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L55">
+        <v>4.77</v>
+      </c>
+      <c r="M55">
+        <v>11.99067336</v>
+      </c>
+      <c r="N55">
+        <v>-7.220673360000003</v>
+      </c>
+      <c r="O55">
+        <v>-1.732961606400001</v>
+      </c>
+      <c r="P55">
+        <v>-5.487711753600002</v>
+      </c>
+      <c r="Q55">
+        <v>-4.067711753600001</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.2575882245345909</v>
+      </c>
+      <c r="T55">
+        <v>2.740541605559988</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.09547420446119129</v>
+      </c>
+      <c r="W55">
+        <v>0.2160007599746675</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.3978091852549638</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2375468683178315</v>
+      </c>
+      <c r="C56">
+        <v>4.61077914414269</v>
+      </c>
+      <c r="D56">
+        <v>45.8703791441427</v>
+      </c>
+      <c r="E56">
+        <v>42.11960000000001</v>
+      </c>
+      <c r="F56">
+        <v>51.15960000000001</v>
+      </c>
+      <c r="G56">
+        <v>9.9</v>
+      </c>
+      <c r="H56">
+        <v>85.7</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>6.19</v>
+      </c>
+      <c r="K56">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L56">
+        <v>4.77</v>
+      </c>
+      <c r="M56">
+        <v>12.21691248</v>
+      </c>
+      <c r="N56">
+        <v>-7.446912480000003</v>
+      </c>
+      <c r="O56">
+        <v>-1.787258995200001</v>
+      </c>
+      <c r="P56">
+        <v>-5.659653484800002</v>
+      </c>
+      <c r="Q56">
+        <v>-4.239653484800002</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.2623444902853428</v>
+      </c>
+      <c r="T56">
+        <v>2.800118596985204</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.09370616363783589</v>
+      </c>
+      <c r="W56">
+        <v>0.2164229681232848</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.3904423484909829</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2395468683178315</v>
+      </c>
+      <c r="C57">
+        <v>3.206381936380339</v>
+      </c>
+      <c r="D57">
+        <v>45.41338193638035</v>
+      </c>
+      <c r="E57">
+        <v>43.06700000000001</v>
+      </c>
+      <c r="F57">
+        <v>52.10700000000001</v>
+      </c>
+      <c r="G57">
+        <v>9.9</v>
+      </c>
+      <c r="H57">
+        <v>85.7</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>6.19</v>
+      </c>
+      <c r="K57">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L57">
+        <v>4.77</v>
+      </c>
+      <c r="M57">
+        <v>12.4431516</v>
+      </c>
+      <c r="N57">
+        <v>-7.673151600000002</v>
+      </c>
+      <c r="O57">
+        <v>-1.841556384</v>
+      </c>
+      <c r="P57">
+        <v>-5.831595216000002</v>
+      </c>
+      <c r="Q57">
+        <v>-4.411595216000001</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.2673121456250172</v>
+      </c>
+      <c r="T57">
+        <v>2.862343454695987</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.09200241520805708</v>
+      </c>
+      <c r="W57">
+        <v>0.216829823248316</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.3833433967002378</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2415468683178315</v>
+      </c>
+      <c r="C58">
+        <v>1.811000842386925</v>
+      </c>
+      <c r="D58">
+        <v>44.96540084238693</v>
+      </c>
+      <c r="E58">
+        <v>44.01440000000001</v>
+      </c>
+      <c r="F58">
+        <v>53.05440000000001</v>
+      </c>
+      <c r="G58">
+        <v>9.9</v>
+      </c>
+      <c r="H58">
+        <v>85.7</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>6.19</v>
+      </c>
+      <c r="K58">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L58">
+        <v>4.77</v>
+      </c>
+      <c r="M58">
+        <v>12.66939072</v>
+      </c>
+      <c r="N58">
+        <v>-7.899390720000003</v>
+      </c>
+      <c r="O58">
+        <v>-1.895853772800001</v>
+      </c>
+      <c r="P58">
+        <v>-6.003536947200002</v>
+      </c>
+      <c r="Q58">
+        <v>-4.583536947200002</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.2725056034801312</v>
+      </c>
+      <c r="T58">
+        <v>2.927396715029987</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.09035951493648461</v>
+      </c>
+      <c r="W58">
+        <v>0.2172221478331675</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.3764979789020193</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2435468683178315</v>
+      </c>
+      <c r="C59">
+        <v>0.4243716496591858</v>
+      </c>
+      <c r="D59">
+        <v>44.5261716496592</v>
+      </c>
+      <c r="E59">
+        <v>44.96180000000001</v>
+      </c>
+      <c r="F59">
+        <v>54.00180000000001</v>
+      </c>
+      <c r="G59">
+        <v>9.9</v>
+      </c>
+      <c r="H59">
+        <v>85.7</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>6.19</v>
+      </c>
+      <c r="K59">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L59">
+        <v>4.77</v>
+      </c>
+      <c r="M59">
+        <v>12.89562984</v>
+      </c>
+      <c r="N59">
+        <v>-8.125629840000004</v>
+      </c>
+      <c r="O59">
+        <v>-1.950151161600001</v>
+      </c>
+      <c r="P59">
+        <v>-6.175478678400003</v>
+      </c>
+      <c r="Q59">
+        <v>-4.755478678400002</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.2779406175145528</v>
+      </c>
+      <c r="T59">
+        <v>2.995475708402777</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.08877426028847611</v>
+      </c>
+      <c r="W59">
+        <v>0.2176007066431119</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.3698927512019838</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2455468683178315</v>
+      </c>
+      <c r="C60">
+        <v>-0.9537596306928577</v>
+      </c>
+      <c r="D60">
+        <v>44.09544036930715</v>
+      </c>
+      <c r="E60">
+        <v>45.90920000000001</v>
+      </c>
+      <c r="F60">
+        <v>54.9492</v>
+      </c>
+      <c r="G60">
+        <v>9.9</v>
+      </c>
+      <c r="H60">
+        <v>85.7</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>6.19</v>
+      </c>
+      <c r="K60">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L60">
+        <v>4.77</v>
+      </c>
+      <c r="M60">
+        <v>13.12186896</v>
+      </c>
+      <c r="N60">
+        <v>-8.351868960000003</v>
+      </c>
+      <c r="O60">
+        <v>-2.004448550400001</v>
+      </c>
+      <c r="P60">
+        <v>-6.347420409600002</v>
+      </c>
+      <c r="Q60">
+        <v>-4.927420409600001</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.2836344417410898</v>
+      </c>
+      <c r="T60">
+        <v>3.066796558602843</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.08724366959384722</v>
+      </c>
+      <c r="W60">
+        <v>0.2179662117009893</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.3635152899743634</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2475468683178315</v>
+      </c>
+      <c r="C61">
+        <v>-2.323637253707247</v>
+      </c>
+      <c r="D61">
+        <v>43.67296274629275</v>
+      </c>
+      <c r="E61">
+        <v>46.8566</v>
+      </c>
+      <c r="F61">
+        <v>55.8966</v>
+      </c>
+      <c r="G61">
+        <v>9.9</v>
+      </c>
+      <c r="H61">
+        <v>85.7</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>6.19</v>
+      </c>
+      <c r="K61">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L61">
+        <v>4.77</v>
+      </c>
+      <c r="M61">
+        <v>13.34810808</v>
+      </c>
+      <c r="N61">
+        <v>-8.578108080000002</v>
+      </c>
+      <c r="O61">
+        <v>-2.0587459392</v>
+      </c>
+      <c r="P61">
+        <v>-6.519362140800001</v>
+      </c>
+      <c r="Q61">
+        <v>-5.0993621408</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.2896060134908724</v>
+      </c>
+      <c r="T61">
+        <v>3.141596474666327</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.08576496332954472</v>
+      </c>
+      <c r="W61">
+        <v>0.2183193267569047</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.3573540138731031</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2495468683178315</v>
+      </c>
+      <c r="C62">
+        <v>-3.685496202444071</v>
+      </c>
+      <c r="D62">
+        <v>43.25850379755593</v>
+      </c>
+      <c r="E62">
+        <v>47.804</v>
+      </c>
+      <c r="F62">
+        <v>56.844</v>
+      </c>
+      <c r="G62">
+        <v>9.9</v>
+      </c>
+      <c r="H62">
+        <v>85.7</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>6.19</v>
+      </c>
+      <c r="K62">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L62">
+        <v>4.77</v>
+      </c>
+      <c r="M62">
+        <v>13.5743472</v>
+      </c>
+      <c r="N62">
+        <v>-8.804347200000002</v>
+      </c>
+      <c r="O62">
+        <v>-2.113043328</v>
+      </c>
+      <c r="P62">
+        <v>-6.691303872000002</v>
+      </c>
+      <c r="Q62">
+        <v>-5.271303872000002</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2958761638281443</v>
+      </c>
+      <c r="T62">
+        <v>3.220136386532985</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.08433554727405232</v>
+      </c>
+      <c r="W62">
+        <v>0.2186606713109563</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.3513981136418847</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2515468683178315</v>
+      </c>
+      <c r="C63">
+        <v>-5.039562623807612</v>
+      </c>
+      <c r="D63">
+        <v>42.85183737619239</v>
+      </c>
+      <c r="E63">
+        <v>48.7514</v>
+      </c>
+      <c r="F63">
+        <v>57.7914</v>
+      </c>
+      <c r="G63">
+        <v>9.9</v>
+      </c>
+      <c r="H63">
+        <v>85.7</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>6.19</v>
+      </c>
+      <c r="K63">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L63">
+        <v>4.77</v>
+      </c>
+      <c r="M63">
+        <v>13.80058632</v>
+      </c>
+      <c r="N63">
+        <v>-9.030586320000001</v>
+      </c>
+      <c r="O63">
+        <v>-2.1673407168</v>
+      </c>
+      <c r="P63">
+        <v>-6.863245603200001</v>
+      </c>
+      <c r="Q63">
+        <v>-5.4432456032</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.3024678603365583</v>
+      </c>
+      <c r="T63">
+        <v>3.302703986187677</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.08295299731873999</v>
+      </c>
+      <c r="W63">
+        <v>0.2189908242402849</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.3456374888280833</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2535468683178315</v>
+      </c>
+      <c r="C64">
+        <v>-6.386054240014751</v>
+      </c>
+      <c r="D64">
+        <v>42.45274575998526</v>
+      </c>
+      <c r="E64">
+        <v>49.69880000000001</v>
+      </c>
+      <c r="F64">
+        <v>58.7388</v>
+      </c>
+      <c r="G64">
+        <v>9.9</v>
+      </c>
+      <c r="H64">
+        <v>85.7</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>6.19</v>
+      </c>
+      <c r="K64">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L64">
+        <v>4.77</v>
+      </c>
+      <c r="M64">
+        <v>14.02682544</v>
+      </c>
+      <c r="N64">
+        <v>-9.256825440000002</v>
+      </c>
+      <c r="O64">
+        <v>-2.2216381056</v>
+      </c>
+      <c r="P64">
+        <v>-7.035187334400002</v>
+      </c>
+      <c r="Q64">
+        <v>-5.615187334400001</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.3094064882401519</v>
+      </c>
+      <c r="T64">
+        <v>3.38961724898209</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.08161504574908289</v>
+      </c>
+      <c r="W64">
+        <v>0.219310327075119</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.3400626906211788</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2555468683178315</v>
+      </c>
+      <c r="C65">
+        <v>-7.725180737282841</v>
+      </c>
+      <c r="D65">
+        <v>42.06101926271717</v>
+      </c>
+      <c r="E65">
+        <v>50.64620000000001</v>
+      </c>
+      <c r="F65">
+        <v>59.68620000000001</v>
+      </c>
+      <c r="G65">
+        <v>9.9</v>
+      </c>
+      <c r="H65">
+        <v>85.7</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>6.19</v>
+      </c>
+      <c r="K65">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L65">
+        <v>4.77</v>
+      </c>
+      <c r="M65">
+        <v>14.25306456</v>
+      </c>
+      <c r="N65">
+        <v>-9.483064560000003</v>
+      </c>
+      <c r="O65">
+        <v>-2.275935494400001</v>
+      </c>
+      <c r="P65">
+        <v>-7.207129065600002</v>
+      </c>
+      <c r="Q65">
+        <v>-5.787129065600001</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.3167201771115074</v>
+      </c>
+      <c r="T65">
+        <v>3.481228525981606</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.08031956883243077</v>
+      </c>
+      <c r="W65">
+        <v>0.2196196869628156</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.3346648701351282</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2575468683178315</v>
+      </c>
+      <c r="C66">
+        <v>-9.057144133194896</v>
+      </c>
+      <c r="D66">
+        <v>41.67645586680511</v>
+      </c>
+      <c r="E66">
+        <v>51.59360000000001</v>
+      </c>
+      <c r="F66">
+        <v>60.63360000000001</v>
+      </c>
+      <c r="G66">
+        <v>9.9</v>
+      </c>
+      <c r="H66">
+        <v>85.7</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>6.19</v>
+      </c>
+      <c r="K66">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L66">
+        <v>4.77</v>
+      </c>
+      <c r="M66">
+        <v>14.47930368</v>
+      </c>
+      <c r="N66">
+        <v>-9.709303680000003</v>
+      </c>
+      <c r="O66">
+        <v>-2.330232883200001</v>
+      </c>
+      <c r="P66">
+        <v>-7.379070796800002</v>
+      </c>
+      <c r="Q66">
+        <v>-5.959070796800002</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.3244401820312715</v>
+      </c>
+      <c r="T66">
+        <v>3.577929318369984</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.07906457556942405</v>
+      </c>
+      <c r="W66">
+        <v>0.2199193793540216</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.3294357315392669</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2595468683178315</v>
+      </c>
+      <c r="C67">
+        <v>-10.38213912409461</v>
+      </c>
+      <c r="D67">
+        <v>41.2988608759054</v>
+      </c>
+      <c r="E67">
+        <v>52.54100000000001</v>
+      </c>
+      <c r="F67">
+        <v>61.58100000000001</v>
+      </c>
+      <c r="G67">
+        <v>9.9</v>
+      </c>
+      <c r="H67">
+        <v>85.7</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>6.19</v>
+      </c>
+      <c r="K67">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L67">
+        <v>4.77</v>
+      </c>
+      <c r="M67">
+        <v>14.7055428</v>
+      </c>
+      <c r="N67">
+        <v>-9.935542800000004</v>
+      </c>
+      <c r="O67">
+        <v>-2.384530272000001</v>
+      </c>
+      <c r="P67">
+        <v>-7.551012528000003</v>
+      </c>
+      <c r="Q67">
+        <v>-6.131012528000002</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.3326013300893078</v>
+      </c>
+      <c r="T67">
+        <v>3.680155870323412</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.0778481974837406</v>
+      </c>
+      <c r="W67">
+        <v>0.2202098504408828</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.3243674895155858</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2615468683178315</v>
+      </c>
+      <c r="C68">
+        <v>-11.70035341376603</v>
+      </c>
+      <c r="D68">
+        <v>40.92804658623398</v>
+      </c>
+      <c r="E68">
+        <v>53.48840000000001</v>
+      </c>
+      <c r="F68">
+        <v>62.52840000000001</v>
+      </c>
+      <c r="G68">
+        <v>9.9</v>
+      </c>
+      <c r="H68">
+        <v>85.7</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>6.19</v>
+      </c>
+      <c r="K68">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L68">
+        <v>4.77</v>
+      </c>
+      <c r="M68">
+        <v>14.93178192</v>
+      </c>
+      <c r="N68">
+        <v>-10.16178192</v>
+      </c>
+      <c r="O68">
+        <v>-2.438827660800001</v>
+      </c>
+      <c r="P68">
+        <v>-7.722954259200003</v>
+      </c>
+      <c r="Q68">
+        <v>-6.302954259200003</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.3412425456801698</v>
+      </c>
+      <c r="T68">
+        <v>3.788395748862337</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.07666867934004755</v>
+      </c>
+      <c r="W68">
+        <v>0.2204915193735967</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.3194528305835315</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2635468683178315</v>
+      </c>
+      <c r="C69">
+        <v>-13.01196802456411</v>
+      </c>
+      <c r="D69">
+        <v>40.5638319754359</v>
+      </c>
+      <c r="E69">
+        <v>54.43580000000001</v>
+      </c>
+      <c r="F69">
+        <v>63.47580000000001</v>
+      </c>
+      <c r="G69">
+        <v>9.9</v>
+      </c>
+      <c r="H69">
+        <v>85.7</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>6.19</v>
+      </c>
+      <c r="K69">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L69">
+        <v>4.77</v>
+      </c>
+      <c r="M69">
+        <v>15.15802104</v>
+      </c>
+      <c r="N69">
+        <v>-10.38802104</v>
+      </c>
+      <c r="O69">
+        <v>-2.493125049600001</v>
+      </c>
+      <c r="P69">
+        <v>-7.894895990400003</v>
+      </c>
+      <c r="Q69">
+        <v>-6.474895990400002</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.3504074713068416</v>
+      </c>
+      <c r="T69">
+        <v>3.903195620039982</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.07552437069318117</v>
+      </c>
+      <c r="W69">
+        <v>0.2207647802784684</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.3146848778882549</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2655468683178315</v>
+      </c>
+      <c r="C70">
+        <v>-14.31715759207936</v>
+      </c>
+      <c r="D70">
+        <v>40.20604240792065</v>
+      </c>
+      <c r="E70">
+        <v>55.38320000000001</v>
+      </c>
+      <c r="F70">
+        <v>64.42320000000001</v>
+      </c>
+      <c r="G70">
+        <v>9.9</v>
+      </c>
+      <c r="H70">
+        <v>85.7</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>6.19</v>
+      </c>
+      <c r="K70">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L70">
+        <v>4.77</v>
+      </c>
+      <c r="M70">
+        <v>15.38426016</v>
+      </c>
+      <c r="N70">
+        <v>-10.61426016</v>
+      </c>
+      <c r="O70">
+        <v>-2.5474224384</v>
+      </c>
+      <c r="P70">
+        <v>-8.066837721600002</v>
+      </c>
+      <c r="Q70">
+        <v>-6.646837721600002</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.3601452047851804</v>
+      </c>
+      <c r="T70">
+        <v>4.025170483166232</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.07441371818298734</v>
+      </c>
+      <c r="W70">
+        <v>0.2210300040979026</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.3100571590957806</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2675468683178315</v>
+      </c>
+      <c r="C71">
+        <v>-15.61609064434442</v>
+      </c>
+      <c r="D71">
+        <v>39.85450935565559</v>
+      </c>
+      <c r="E71">
+        <v>56.33060000000001</v>
+      </c>
+      <c r="F71">
+        <v>65.37060000000001</v>
+      </c>
+      <c r="G71">
+        <v>9.9</v>
+      </c>
+      <c r="H71">
+        <v>85.7</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>6.19</v>
+      </c>
+      <c r="K71">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L71">
+        <v>4.77</v>
+      </c>
+      <c r="M71">
+        <v>15.61049928</v>
+      </c>
+      <c r="N71">
+        <v>-10.84049928</v>
+      </c>
+      <c r="O71">
+        <v>-2.601719827200001</v>
+      </c>
+      <c r="P71">
+        <v>-8.238779452800003</v>
+      </c>
+      <c r="Q71">
+        <v>-6.818779452800002</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.3705111791330895</v>
+      </c>
+      <c r="T71">
+        <v>4.155014692300627</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.07333525849917592</v>
+      </c>
+      <c r="W71">
+        <v>0.2212875402703968</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.3055635770798997</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2695468683178315</v>
+      </c>
+      <c r="C72">
+        <v>-16.90892986652065</v>
+      </c>
+      <c r="D72">
+        <v>39.50907013347936</v>
+      </c>
+      <c r="E72">
+        <v>57.27800000000001</v>
+      </c>
+      <c r="F72">
+        <v>66.31800000000001</v>
+      </c>
+      <c r="G72">
+        <v>9.9</v>
+      </c>
+      <c r="H72">
+        <v>85.7</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>6.19</v>
+      </c>
+      <c r="K72">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L72">
+        <v>4.77</v>
+      </c>
+      <c r="M72">
+        <v>15.8367384</v>
+      </c>
+      <c r="N72">
+        <v>-11.0667384</v>
+      </c>
+      <c r="O72">
+        <v>-2.656017216000001</v>
+      </c>
+      <c r="P72">
+        <v>-8.410721184000003</v>
+      </c>
+      <c r="Q72">
+        <v>-6.990721184000003</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.3815682184375258</v>
+      </c>
+      <c r="T72">
+        <v>4.293515182043981</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.07228761194918769</v>
+      </c>
+      <c r="W72">
+        <v>0.221537718266534</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.3011983831216154</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2715468683178315</v>
+      </c>
+      <c r="C73">
+        <v>-18.19583235193776</v>
+      </c>
+      <c r="D73">
+        <v>39.16956764806224</v>
+      </c>
+      <c r="E73">
+        <v>58.2254</v>
+      </c>
+      <c r="F73">
+        <v>67.2654</v>
+      </c>
+      <c r="G73">
+        <v>9.9</v>
+      </c>
+      <c r="H73">
+        <v>85.7</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>6.19</v>
+      </c>
+      <c r="K73">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L73">
+        <v>4.77</v>
+      </c>
+      <c r="M73">
+        <v>16.06297752</v>
+      </c>
+      <c r="N73">
+        <v>-11.29297752</v>
+      </c>
+      <c r="O73">
+        <v>-2.7103146048</v>
+      </c>
+      <c r="P73">
+        <v>-8.5826629152</v>
+      </c>
+      <c r="Q73">
+        <v>-7.162662915199999</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.3933878121767507</v>
+      </c>
+      <c r="T73">
+        <v>4.441567429700669</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.07126947656962168</v>
+      </c>
+      <c r="W73">
+        <v>0.2217808489951744</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.2969561523734237</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2735468683178315</v>
+      </c>
+      <c r="C74">
+        <v>-19.47694984030084</v>
+      </c>
+      <c r="D74">
+        <v>38.83585015969916</v>
+      </c>
+      <c r="E74">
+        <v>59.1728</v>
+      </c>
+      <c r="F74">
+        <v>68.2128</v>
+      </c>
+      <c r="G74">
+        <v>9.9</v>
+      </c>
+      <c r="H74">
+        <v>85.7</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>6.19</v>
+      </c>
+      <c r="K74">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L74">
+        <v>4.77</v>
+      </c>
+      <c r="M74">
+        <v>16.28921664</v>
+      </c>
+      <c r="N74">
+        <v>-11.51921664</v>
+      </c>
+      <c r="O74">
+        <v>-2.764611993600001</v>
+      </c>
+      <c r="P74">
+        <v>-8.754604646400002</v>
+      </c>
+      <c r="Q74">
+        <v>-7.334604646400002</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.4060516626116347</v>
+      </c>
+      <c r="T74">
+        <v>4.600194837904264</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.07027962272837693</v>
+      </c>
+      <c r="W74">
+        <v>0.2220172260924636</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.2928317613682372</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2755468683178315</v>
+      </c>
+      <c r="C75">
+        <v>-20.75242894382303</v>
+      </c>
+      <c r="D75">
+        <v>38.50777105617698</v>
+      </c>
+      <c r="E75">
+        <v>60.1202</v>
+      </c>
+      <c r="F75">
+        <v>69.1602</v>
+      </c>
+      <c r="G75">
+        <v>9.9</v>
+      </c>
+      <c r="H75">
+        <v>85.7</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>6.19</v>
+      </c>
+      <c r="K75">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L75">
+        <v>4.77</v>
+      </c>
+      <c r="M75">
+        <v>16.51545576</v>
+      </c>
+      <c r="N75">
+        <v>-11.74545576</v>
+      </c>
+      <c r="O75">
+        <v>-2.8189093824</v>
+      </c>
+      <c r="P75">
+        <v>-8.926546377600001</v>
+      </c>
+      <c r="Q75">
+        <v>-7.5065463776</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.4196535760416952</v>
+      </c>
+      <c r="T75">
+        <v>4.770572424493311</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.06931688817045396</v>
+      </c>
+      <c r="W75">
+        <v>0.2222471271048956</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.2888203673768915</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2775468683178315</v>
+      </c>
+      <c r="C76">
+        <v>-22.0224113619925</v>
+      </c>
+      <c r="D76">
+        <v>38.18518863800751</v>
+      </c>
+      <c r="E76">
+        <v>61.06760000000001</v>
+      </c>
+      <c r="F76">
+        <v>70.10760000000001</v>
+      </c>
+      <c r="G76">
+        <v>9.9</v>
+      </c>
+      <c r="H76">
+        <v>85.7</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>6.19</v>
+      </c>
+      <c r="K76">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L76">
+        <v>4.77</v>
+      </c>
+      <c r="M76">
+        <v>16.74169488</v>
+      </c>
+      <c r="N76">
+        <v>-11.97169488</v>
+      </c>
+      <c r="O76">
+        <v>-2.8732067712</v>
+      </c>
+      <c r="P76">
+        <v>-9.098488108800002</v>
+      </c>
+      <c r="Q76">
+        <v>-7.678488108800001</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.4343017905048374</v>
+      </c>
+      <c r="T76">
+        <v>4.954055979281516</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.06838017346544782</v>
+      </c>
+      <c r="W76">
+        <v>0.2224708145764511</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.284917389439366</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2795468683178315</v>
+      </c>
+      <c r="C77">
+        <v>-23.2870340856343</v>
+      </c>
+      <c r="D77">
+        <v>37.8679659143657</v>
+      </c>
+      <c r="E77">
+        <v>62.01500000000001</v>
+      </c>
+      <c r="F77">
+        <v>71.05500000000001</v>
+      </c>
+      <c r="G77">
+        <v>9.9</v>
+      </c>
+      <c r="H77">
+        <v>85.7</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>6.19</v>
+      </c>
+      <c r="K77">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L77">
+        <v>4.77</v>
+      </c>
+      <c r="M77">
+        <v>16.967934</v>
+      </c>
+      <c r="N77">
+        <v>-12.197934</v>
+      </c>
+      <c r="O77">
+        <v>-2.927504160000001</v>
+      </c>
+      <c r="P77">
+        <v>-9.270429840000002</v>
+      </c>
+      <c r="Q77">
+        <v>-7.850429840000001</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.4501218621250309</v>
+      </c>
+      <c r="T77">
+        <v>5.152218218452777</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.06746843781924185</v>
+      </c>
+      <c r="W77">
+        <v>0.2226885370487651</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.2811184909135077</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2815468683178315</v>
+      </c>
+      <c r="C78">
+        <v>-24.54642959088452</v>
+      </c>
+      <c r="D78">
+        <v>37.55597040911549</v>
+      </c>
+      <c r="E78">
+        <v>62.96240000000001</v>
+      </c>
+      <c r="F78">
+        <v>72.00240000000001</v>
+      </c>
+      <c r="G78">
+        <v>9.9</v>
+      </c>
+      <c r="H78">
+        <v>85.7</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>6.19</v>
+      </c>
+      <c r="K78">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L78">
+        <v>4.77</v>
+      </c>
+      <c r="M78">
+        <v>17.19417312</v>
+      </c>
+      <c r="N78">
+        <v>-12.42417312</v>
+      </c>
+      <c r="O78">
+        <v>-2.9818015488</v>
+      </c>
+      <c r="P78">
+        <v>-9.442371571200002</v>
+      </c>
+      <c r="Q78">
+        <v>-8.022371571200001</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.4672602730469071</v>
+      </c>
+      <c r="T78">
+        <v>5.366893977554976</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.06658069521635709</v>
+      </c>
+      <c r="W78">
+        <v>0.2229005299823339</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.2774195634014879</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2835468683178315</v>
+      </c>
+      <c r="C79">
+        <v>-25.80072602365395</v>
+      </c>
+      <c r="D79">
+        <v>37.24907397634606</v>
+      </c>
+      <c r="E79">
+        <v>63.90980000000001</v>
+      </c>
+      <c r="F79">
+        <v>72.94980000000001</v>
+      </c>
+      <c r="G79">
+        <v>9.9</v>
+      </c>
+      <c r="H79">
+        <v>85.7</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>6.19</v>
+      </c>
+      <c r="K79">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L79">
+        <v>4.77</v>
+      </c>
+      <c r="M79">
+        <v>17.42041224</v>
+      </c>
+      <c r="N79">
+        <v>-12.65041224</v>
+      </c>
+      <c r="O79">
+        <v>-3.036098937600001</v>
+      </c>
+      <c r="P79">
+        <v>-9.614313302400003</v>
+      </c>
+      <c r="Q79">
+        <v>-8.194313302400001</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.4858889805706856</v>
+      </c>
+      <c r="T79">
+        <v>5.600237193970409</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.0657160108628979</v>
+      </c>
+      <c r="W79">
+        <v>0.22310701660594</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.2738167119287412</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2855468683178315</v>
+      </c>
+      <c r="C80">
+        <v>-27.05004737512065</v>
+      </c>
+      <c r="D80">
+        <v>36.94715262487937</v>
+      </c>
+      <c r="E80">
+        <v>64.85720000000001</v>
+      </c>
+      <c r="F80">
+        <v>73.89720000000001</v>
+      </c>
+      <c r="G80">
+        <v>9.9</v>
+      </c>
+      <c r="H80">
+        <v>85.7</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>6.19</v>
+      </c>
+      <c r="K80">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L80">
+        <v>4.77</v>
+      </c>
+      <c r="M80">
+        <v>17.64665136</v>
+      </c>
+      <c r="N80">
+        <v>-12.87665136</v>
+      </c>
+      <c r="O80">
+        <v>-3.090396326400001</v>
+      </c>
+      <c r="P80">
+        <v>-9.786255033600003</v>
+      </c>
+      <c r="Q80">
+        <v>-8.366255033600002</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.5062112069602624</v>
+      </c>
+      <c r="T80">
+        <v>5.854793430059975</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.06487349790311717</v>
+      </c>
+      <c r="W80">
+        <v>0.2233082087007356</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.2703062412629882</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2875468683178315</v>
+      </c>
+      <c r="C81">
+        <v>-28.29451364875647</v>
+      </c>
+      <c r="D81">
+        <v>36.65008635124354</v>
+      </c>
+      <c r="E81">
+        <v>65.80460000000002</v>
+      </c>
+      <c r="F81">
+        <v>74.84460000000001</v>
+      </c>
+      <c r="G81">
+        <v>9.9</v>
+      </c>
+      <c r="H81">
+        <v>85.7</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>6.19</v>
+      </c>
+      <c r="K81">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L81">
+        <v>4.77</v>
+      </c>
+      <c r="M81">
+        <v>17.87289048000001</v>
+      </c>
+      <c r="N81">
+        <v>-13.10289048000001</v>
+      </c>
+      <c r="O81">
+        <v>-3.144693715200001</v>
+      </c>
+      <c r="P81">
+        <v>-9.958196764800006</v>
+      </c>
+      <c r="Q81">
+        <v>-8.538196764800006</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.5284688834821798</v>
+      </c>
+      <c r="T81">
+        <v>6.133593117205688</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.06405231438535618</v>
+      </c>
+      <c r="W81">
+        <v>0.2235043073247769</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.2668846432723174</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2895468683178315</v>
+      </c>
+      <c r="C82">
+        <v>-29.53424101936026</v>
+      </c>
+      <c r="D82">
+        <v>36.35775898063976</v>
+      </c>
+      <c r="E82">
+        <v>66.75200000000001</v>
+      </c>
+      <c r="F82">
+        <v>75.79200000000002</v>
+      </c>
+      <c r="G82">
+        <v>9.9</v>
+      </c>
+      <c r="H82">
+        <v>85.7</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>6.19</v>
+      </c>
+      <c r="K82">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L82">
+        <v>4.77</v>
+      </c>
+      <c r="M82">
+        <v>18.0991296</v>
+      </c>
+      <c r="N82">
+        <v>-13.32912960000001</v>
+      </c>
+      <c r="O82">
+        <v>-3.198991104000001</v>
+      </c>
+      <c r="P82">
+        <v>-10.130138496</v>
+      </c>
+      <c r="Q82">
+        <v>-8.710138496000003</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.5529523276562887</v>
+      </c>
+      <c r="T82">
+        <v>6.440272773065972</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.06325166045553922</v>
+      </c>
+      <c r="W82">
+        <v>0.2236955034832173</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.2635485852314134</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2915468683178315</v>
+      </c>
+      <c r="C83">
+        <v>-30.76934198454033</v>
+      </c>
+      <c r="D83">
+        <v>36.07005801545969</v>
+      </c>
+      <c r="E83">
+        <v>67.69940000000003</v>
+      </c>
+      <c r="F83">
+        <v>76.73940000000002</v>
+      </c>
+      <c r="G83">
+        <v>9.9</v>
+      </c>
+      <c r="H83">
+        <v>85.7</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>6.19</v>
+      </c>
+      <c r="K83">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L83">
+        <v>4.77</v>
+      </c>
+      <c r="M83">
+        <v>18.32536872</v>
+      </c>
+      <c r="N83">
+        <v>-13.55536872</v>
+      </c>
+      <c r="O83">
+        <v>-3.253288492800001</v>
+      </c>
+      <c r="P83">
+        <v>-10.3020802272</v>
+      </c>
+      <c r="Q83">
+        <v>-8.882080227200003</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.5800129764803039</v>
+      </c>
+      <c r="T83">
+        <v>6.779234497964181</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.06247077575855726</v>
+      </c>
+      <c r="W83">
+        <v>0.2238819787488565</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.2602948989939886</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2935468683178315</v>
+      </c>
+      <c r="C84">
+        <v>-31.99992550906128</v>
+      </c>
+      <c r="D84">
+        <v>35.78687449093874</v>
+      </c>
+      <c r="E84">
+        <v>68.64680000000001</v>
+      </c>
+      <c r="F84">
+        <v>77.68680000000002</v>
+      </c>
+      <c r="G84">
+        <v>9.9</v>
+      </c>
+      <c r="H84">
+        <v>85.7</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>6.19</v>
+      </c>
+      <c r="K84">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L84">
+        <v>4.77</v>
+      </c>
+      <c r="M84">
+        <v>18.55160784000001</v>
+      </c>
+      <c r="N84">
+        <v>-13.78160784000001</v>
+      </c>
+      <c r="O84">
+        <v>-3.307585881600001</v>
+      </c>
+      <c r="P84">
+        <v>-10.47402195840001</v>
+      </c>
+      <c r="Q84">
+        <v>-9.054021958400003</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.610080364062543</v>
+      </c>
+      <c r="T84">
+        <v>7.155858636739969</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.06170893702979437</v>
+      </c>
+      <c r="W84">
+        <v>0.2240639058372851</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.2571205709574765</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2955468683178316</v>
+      </c>
+      <c r="C85">
+        <v>-33.22609716244432</v>
+      </c>
+      <c r="D85">
+        <v>35.5081028375557</v>
+      </c>
+      <c r="E85">
+        <v>69.59420000000003</v>
+      </c>
+      <c r="F85">
+        <v>78.63420000000002</v>
+      </c>
+      <c r="G85">
+        <v>9.9</v>
+      </c>
+      <c r="H85">
+        <v>85.7</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>6.19</v>
+      </c>
+      <c r="K85">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L85">
+        <v>4.77</v>
+      </c>
+      <c r="M85">
+        <v>18.77784696000001</v>
+      </c>
+      <c r="N85">
+        <v>-14.00784696000001</v>
+      </c>
+      <c r="O85">
+        <v>-3.361883270400001</v>
+      </c>
+      <c r="P85">
+        <v>-10.6459636896</v>
+      </c>
+      <c r="Q85">
+        <v>-9.225963689600004</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.6436850913603398</v>
+      </c>
+      <c r="T85">
+        <v>7.576791497724674</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.06096545586076071</v>
+      </c>
+      <c r="W85">
+        <v>0.2242414491404504</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.2540227327531696</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2975468683178315</v>
+      </c>
+      <c r="C86">
+        <v>-34.4479592501859</v>
+      </c>
+      <c r="D86">
+        <v>35.23364074981411</v>
+      </c>
+      <c r="E86">
+        <v>70.54160000000002</v>
+      </c>
+      <c r="F86">
+        <v>79.58160000000001</v>
+      </c>
+      <c r="G86">
+        <v>9.9</v>
+      </c>
+      <c r="H86">
+        <v>85.7</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>6.19</v>
+      </c>
+      <c r="K86">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L86">
+        <v>4.77</v>
+      </c>
+      <c r="M86">
+        <v>19.00408608</v>
+      </c>
+      <c r="N86">
+        <v>-14.23408608</v>
+      </c>
+      <c r="O86">
+        <v>-3.416180659200001</v>
+      </c>
+      <c r="P86">
+        <v>-10.8179054208</v>
+      </c>
+      <c r="Q86">
+        <v>-9.397905420800001</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.6814904095703607</v>
+      </c>
+      <c r="T86">
+        <v>8.050340966332463</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.06023967662432309</v>
+      </c>
+      <c r="W86">
+        <v>0.2244147652221117</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.2509986526013461</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2995468683178315</v>
+      </c>
+      <c r="C87">
+        <v>-35.66561093893767</v>
+      </c>
+      <c r="D87">
+        <v>34.96338906106234</v>
+      </c>
+      <c r="E87">
+        <v>71.489</v>
+      </c>
+      <c r="F87">
+        <v>80.52900000000001</v>
+      </c>
+      <c r="G87">
+        <v>9.9</v>
+      </c>
+      <c r="H87">
+        <v>85.7</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>6.19</v>
+      </c>
+      <c r="K87">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L87">
+        <v>4.77</v>
+      </c>
+      <c r="M87">
+        <v>19.2303252</v>
+      </c>
+      <c r="N87">
+        <v>-14.4603252</v>
+      </c>
+      <c r="O87">
+        <v>-3.470478048000001</v>
+      </c>
+      <c r="P87">
+        <v>-10.989847152</v>
+      </c>
+      <c r="Q87">
+        <v>-9.569847152000001</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.7243364368750513</v>
+      </c>
+      <c r="T87">
+        <v>8.58703036408796</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.05953097454638987</v>
+      </c>
+      <c r="W87">
+        <v>0.2245840032783221</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.2480457272766244</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.3015468683178315</v>
+      </c>
+      <c r="C88">
+        <v>-36.87914837596904</v>
+      </c>
+      <c r="D88">
+        <v>34.69725162403098</v>
+      </c>
+      <c r="E88">
+        <v>72.43640000000002</v>
+      </c>
+      <c r="F88">
+        <v>81.47640000000001</v>
+      </c>
+      <c r="G88">
+        <v>9.9</v>
+      </c>
+      <c r="H88">
+        <v>85.7</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>6.19</v>
+      </c>
+      <c r="K88">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L88">
+        <v>4.77</v>
+      </c>
+      <c r="M88">
+        <v>19.45656432000001</v>
+      </c>
+      <c r="N88">
+        <v>-14.68656432000001</v>
+      </c>
+      <c r="O88">
+        <v>-3.524775436800001</v>
+      </c>
+      <c r="P88">
+        <v>-11.16178888320001</v>
+      </c>
+      <c r="Q88">
+        <v>-9.741788883200005</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.7733033252232693</v>
+      </c>
+      <c r="T88">
+        <v>9.200389675808529</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.05883875391212952</v>
+      </c>
+      <c r="W88">
+        <v>0.2247493055657835</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.2451614746338729</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.3035468683178315</v>
+      </c>
+      <c r="C89">
+        <v>-38.08866480321512</v>
+      </c>
+      <c r="D89">
+        <v>34.43513519678489</v>
+      </c>
+      <c r="E89">
+        <v>73.38380000000001</v>
+      </c>
+      <c r="F89">
+        <v>82.42380000000001</v>
+      </c>
+      <c r="G89">
+        <v>9.9</v>
+      </c>
+      <c r="H89">
+        <v>85.7</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>6.19</v>
+      </c>
+      <c r="K89">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L89">
+        <v>4.77</v>
+      </c>
+      <c r="M89">
+        <v>19.68280344</v>
+      </c>
+      <c r="N89">
+        <v>-14.91280344</v>
+      </c>
+      <c r="O89">
+        <v>-3.579072825600001</v>
+      </c>
+      <c r="P89">
+        <v>-11.3337306144</v>
+      </c>
+      <c r="Q89">
+        <v>-9.913730614400002</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.8298035810096747</v>
+      </c>
+      <c r="T89">
+        <v>9.908111958563032</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.05816244639589815</v>
+      </c>
+      <c r="W89">
+        <v>0.2249108078006595</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.2423435266495756</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.3055468683178315</v>
+      </c>
+      <c r="C90">
+        <v>-39.29425066619405</v>
+      </c>
+      <c r="D90">
+        <v>34.17694933380595</v>
+      </c>
+      <c r="E90">
+        <v>74.3312</v>
+      </c>
+      <c r="F90">
+        <v>83.3712</v>
+      </c>
+      <c r="G90">
+        <v>9.9</v>
+      </c>
+      <c r="H90">
+        <v>85.7</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>6.19</v>
+      </c>
+      <c r="K90">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L90">
+        <v>4.77</v>
+      </c>
+      <c r="M90">
+        <v>19.90904256</v>
+      </c>
+      <c r="N90">
+        <v>-15.13904256</v>
+      </c>
+      <c r="O90">
+        <v>-3.633370214400001</v>
+      </c>
+      <c r="P90">
+        <v>-11.5056723456</v>
+      </c>
+      <c r="Q90">
+        <v>-10.0856723456</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.8957205460938142</v>
+      </c>
+      <c r="T90">
+        <v>10.73378795510995</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.05750150950503567</v>
+      </c>
+      <c r="W90">
+        <v>0.2250686395301975</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.2395896229376486</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.3075468683178315</v>
+      </c>
+      <c r="C91">
+        <v>-40.49599371806089</v>
+      </c>
+      <c r="D91">
+        <v>33.92260628193911</v>
+      </c>
+      <c r="E91">
+        <v>75.27860000000001</v>
+      </c>
+      <c r="F91">
+        <v>84.3186</v>
+      </c>
+      <c r="G91">
+        <v>9.9</v>
+      </c>
+      <c r="H91">
+        <v>85.7</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>6.19</v>
+      </c>
+      <c r="K91">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L91">
+        <v>4.77</v>
+      </c>
+      <c r="M91">
+        <v>20.13528168</v>
+      </c>
+      <c r="N91">
+        <v>-15.36528168</v>
+      </c>
+      <c r="O91">
+        <v>-3.6876676032</v>
+      </c>
+      <c r="P91">
+        <v>-11.6776140768</v>
+      </c>
+      <c r="Q91">
+        <v>-10.2576140768</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.973622413920525</v>
+      </c>
+      <c r="T91">
+        <v>11.70958686011995</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.0568554251285746</v>
+      </c>
+      <c r="W91">
+        <v>0.2252229244792964</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.2368976047023942</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.3095468683178315</v>
+      </c>
+      <c r="C92">
+        <v>-41.69397911904967</v>
+      </c>
+      <c r="D92">
+        <v>33.67202088095033</v>
+      </c>
+      <c r="E92">
+        <v>76.226</v>
+      </c>
+      <c r="F92">
+        <v>85.26600000000001</v>
+      </c>
+      <c r="G92">
+        <v>9.9</v>
+      </c>
+      <c r="H92">
+        <v>85.7</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>6.19</v>
+      </c>
+      <c r="K92">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L92">
+        <v>4.77</v>
+      </c>
+      <c r="M92">
+        <v>20.3615208</v>
+      </c>
+      <c r="N92">
+        <v>-15.5915208</v>
+      </c>
+      <c r="O92">
+        <v>-3.741964992</v>
+      </c>
+      <c r="P92">
+        <v>-11.849555808</v>
+      </c>
+      <c r="Q92">
+        <v>-10.429555808</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>1.067104655312577</v>
+      </c>
+      <c r="T92">
+        <v>12.88054554613194</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.05622369818270154</v>
+      </c>
+      <c r="W92">
+        <v>0.2253737808739709</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.2342654090945898</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.3115468683178315</v>
+      </c>
+      <c r="C93">
+        <v>-42.88828953154037</v>
+      </c>
+      <c r="D93">
+        <v>33.42511046845964</v>
+      </c>
+      <c r="E93">
+        <v>77.17340000000002</v>
+      </c>
+      <c r="F93">
+        <v>86.21340000000001</v>
+      </c>
+      <c r="G93">
+        <v>9.9</v>
+      </c>
+      <c r="H93">
+        <v>85.7</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>6.19</v>
+      </c>
+      <c r="K93">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L93">
+        <v>4.77</v>
+      </c>
+      <c r="M93">
+        <v>20.58775992</v>
+      </c>
+      <c r="N93">
+        <v>-15.81775992</v>
+      </c>
+      <c r="O93">
+        <v>-3.796262380800001</v>
+      </c>
+      <c r="P93">
+        <v>-12.0214975392</v>
+      </c>
+      <c r="Q93">
+        <v>-10.6014975392</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>1.181360728125086</v>
+      </c>
+      <c r="T93">
+        <v>14.31171727347994</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.055605855345529</v>
+      </c>
+      <c r="W93">
+        <v>0.2255213217434877</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.2316910639397042</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.3135468683178315</v>
+      </c>
+      <c r="C94">
+        <v>-44.07900521097365</v>
+      </c>
+      <c r="D94">
+        <v>33.18179478902636</v>
+      </c>
+      <c r="E94">
+        <v>78.1208</v>
+      </c>
+      <c r="F94">
+        <v>87.16080000000001</v>
+      </c>
+      <c r="G94">
+        <v>9.9</v>
+      </c>
+      <c r="H94">
+        <v>85.7</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>6.19</v>
+      </c>
+      <c r="K94">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L94">
+        <v>4.77</v>
+      </c>
+      <c r="M94">
+        <v>20.81399904</v>
+      </c>
+      <c r="N94">
+        <v>-16.04399904</v>
+      </c>
+      <c r="O94">
+        <v>-3.850559769600001</v>
+      </c>
+      <c r="P94">
+        <v>-12.1934392704</v>
+      </c>
+      <c r="Q94">
+        <v>-10.7734392704</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>1.324180819140722</v>
+      </c>
+      <c r="T94">
+        <v>16.10068193266494</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.05500144387438195</v>
+      </c>
+      <c r="W94">
+        <v>0.2256656552027976</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.2291726828099248</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.3155468683178315</v>
+      </c>
+      <c r="C95">
+        <v>-45.26620409282346</v>
+      </c>
+      <c r="D95">
+        <v>32.94199590717655</v>
+      </c>
+      <c r="E95">
+        <v>79.06820000000002</v>
+      </c>
+      <c r="F95">
+        <v>88.10820000000001</v>
+      </c>
+      <c r="G95">
+        <v>9.9</v>
+      </c>
+      <c r="H95">
+        <v>85.7</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>6.19</v>
+      </c>
+      <c r="K95">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L95">
+        <v>4.77</v>
+      </c>
+      <c r="M95">
+        <v>21.04023816</v>
+      </c>
+      <c r="N95">
+        <v>-16.27023816000001</v>
+      </c>
+      <c r="O95">
+        <v>-3.904857158400001</v>
+      </c>
+      <c r="P95">
+        <v>-12.3653810016</v>
+      </c>
+      <c r="Q95">
+        <v>-10.9453810016</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.50780665044654</v>
+      </c>
+      <c r="T95">
+        <v>18.40077935161707</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.05441003049938859</v>
+      </c>
+      <c r="W95">
+        <v>0.225806884716746</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.2267084604141191</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.3175468683178315</v>
+      </c>
+      <c r="C96">
+        <v>-46.44996187582546</v>
+      </c>
+      <c r="D96">
+        <v>32.70563812417456</v>
+      </c>
+      <c r="E96">
+        <v>80.01560000000001</v>
+      </c>
+      <c r="F96">
+        <v>89.05560000000001</v>
+      </c>
+      <c r="G96">
+        <v>9.9</v>
+      </c>
+      <c r="H96">
+        <v>85.7</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>6.19</v>
+      </c>
+      <c r="K96">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L96">
+        <v>4.77</v>
+      </c>
+      <c r="M96">
+        <v>21.26647728</v>
+      </c>
+      <c r="N96">
+        <v>-16.49647728</v>
+      </c>
+      <c r="O96">
+        <v>-3.959154547200001</v>
+      </c>
+      <c r="P96">
+        <v>-12.5373227328</v>
+      </c>
+      <c r="Q96">
+        <v>-11.1173227328</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.75264109218763</v>
+      </c>
+      <c r="T96">
+        <v>21.46757591021992</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.05383120038769296</v>
+      </c>
+      <c r="W96">
+        <v>0.2259451093474189</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.2242966682820541</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.3195468683178315</v>
+      </c>
+      <c r="C97">
+        <v>-47.63035210164803</v>
+      </c>
+      <c r="D97">
+        <v>32.47264789835199</v>
+      </c>
+      <c r="E97">
+        <v>80.96300000000002</v>
+      </c>
+      <c r="F97">
+        <v>90.00300000000001</v>
+      </c>
+      <c r="G97">
+        <v>9.9</v>
+      </c>
+      <c r="H97">
+        <v>85.7</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>6.19</v>
+      </c>
+      <c r="K97">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L97">
+        <v>4.77</v>
+      </c>
+      <c r="M97">
+        <v>21.49271640000001</v>
+      </c>
+      <c r="N97">
+        <v>-16.72271640000001</v>
+      </c>
+      <c r="O97">
+        <v>-4.013451936000002</v>
+      </c>
+      <c r="P97">
+        <v>-12.709264464</v>
+      </c>
+      <c r="Q97">
+        <v>-11.289264464</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>2.095409310625158</v>
+      </c>
+      <c r="T97">
+        <v>25.76109109226392</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.05326455617308567</v>
+      </c>
+      <c r="W97">
+        <v>0.2260804239858671</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.2219356507211903</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.3215468683178315</v>
+      </c>
+      <c r="C98">
+        <v>-48.80744623118193</v>
+      </c>
+      <c r="D98">
+        <v>32.24295376881807</v>
+      </c>
+      <c r="E98">
+        <v>81.91040000000001</v>
+      </c>
+      <c r="F98">
+        <v>90.9504</v>
+      </c>
+      <c r="G98">
+        <v>9.9</v>
+      </c>
+      <c r="H98">
+        <v>85.7</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>6.19</v>
+      </c>
+      <c r="K98">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L98">
+        <v>4.77</v>
+      </c>
+      <c r="M98">
+        <v>21.71895552</v>
+      </c>
+      <c r="N98">
+        <v>-16.94895552</v>
+      </c>
+      <c r="O98">
+        <v>-4.0677493248</v>
+      </c>
+      <c r="P98">
+        <v>-12.8812061952</v>
+      </c>
+      <c r="Q98">
+        <v>-11.4612061952</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>2.609561638281441</v>
+      </c>
+      <c r="T98">
+        <v>32.20136386532982</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.0527097170462827</v>
+      </c>
+      <c r="W98">
+        <v>0.2262129195693477</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.2196238210261779</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.3235468683178315</v>
+      </c>
+      <c r="C99">
+        <v>-49.98131371761503</v>
+      </c>
+      <c r="D99">
+        <v>32.01648628238497</v>
+      </c>
+      <c r="E99">
+        <v>82.8578</v>
+      </c>
+      <c r="F99">
+        <v>91.8978</v>
+      </c>
+      <c r="G99">
+        <v>9.9</v>
+      </c>
+      <c r="H99">
+        <v>85.7</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>6.19</v>
+      </c>
+      <c r="K99">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L99">
+        <v>4.77</v>
+      </c>
+      <c r="M99">
+        <v>21.94519464</v>
+      </c>
+      <c r="N99">
+        <v>-17.17519464</v>
+      </c>
+      <c r="O99">
+        <v>-4.1220467136</v>
+      </c>
+      <c r="P99">
+        <v>-13.0531479264</v>
+      </c>
+      <c r="Q99">
+        <v>-11.6331479264</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>3.466482184375255</v>
+      </c>
+      <c r="T99">
+        <v>42.93515182043978</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.05216631790147567</v>
+      </c>
+      <c r="W99">
+        <v>0.2263426832851276</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.2173596579228153</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.3255468683178315</v>
+      </c>
+      <c r="C100">
+        <v>-51.15202207644876</v>
+      </c>
+      <c r="D100">
+        <v>31.79317792355124</v>
+      </c>
+      <c r="E100">
+        <v>83.80520000000001</v>
+      </c>
+      <c r="F100">
+        <v>92.84520000000001</v>
+      </c>
+      <c r="G100">
+        <v>9.9</v>
+      </c>
+      <c r="H100">
+        <v>85.7</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>6.19</v>
+      </c>
+      <c r="K100">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L100">
+        <v>4.77</v>
+      </c>
+      <c r="M100">
+        <v>22.17143376</v>
+      </c>
+      <c r="N100">
+        <v>-17.40143376</v>
+      </c>
+      <c r="O100">
+        <v>-4.176344102400001</v>
+      </c>
+      <c r="P100">
+        <v>-13.2250896576</v>
+      </c>
+      <c r="Q100">
+        <v>-11.8050896576</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>5.180323276562881</v>
+      </c>
+      <c r="T100">
+        <v>64.40272773065965</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.05163400853513407</v>
+      </c>
+      <c r="W100">
+        <v>0.22646979876181</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.2151417022297253</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.3275468683178315</v>
+      </c>
+      <c r="C101">
+        <v>-52.31963695260497</v>
+      </c>
+      <c r="D101">
+        <v>31.57296304739504</v>
+      </c>
+      <c r="E101">
+        <v>84.7526</v>
+      </c>
+      <c r="F101">
+        <v>93.79260000000001</v>
+      </c>
+      <c r="G101">
+        <v>9.9</v>
+      </c>
+      <c r="H101">
+        <v>85.7</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>6.19</v>
+      </c>
+      <c r="K101">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="L101">
+        <v>4.77</v>
+      </c>
+      <c r="M101">
+        <v>22.39767288</v>
+      </c>
+      <c r="N101">
+        <v>-17.62767288</v>
+      </c>
+      <c r="O101">
+        <v>-4.2306414912</v>
+      </c>
+      <c r="P101">
+        <v>-13.3970313888</v>
+      </c>
+      <c r="Q101">
+        <v>-11.9770313888</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>10.32184655312576</v>
+      </c>
+      <c r="T101">
+        <v>128.8054554613193</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.05111245289336504</v>
+      </c>
+      <c r="W101">
+        <v>0.2265943462490644</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.2129685537223543</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
